--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/His.&amp;.Hers.S01.2160p.NF.WEB-DL.H.265/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FC3097-544F-D647-944C-3814E2B48EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F095A17B-38E7-E14F-94C7-638EA585E4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1972,9 +1972,6 @@
     <t>https://static.tildacdn.com/stor3939-3739-4134-a436-376362613261/19296733.jpg</t>
   </si>
   <si>
-    <t>https://static.tildacdn.com/stor6566-6433-4163-b464-613937346430/58702522.jpg</t>
-  </si>
-  <si>
     <t>https://static.tildacdn.com/stor3137-3265-4064-a566-386164353061/79893346.jpg</t>
   </si>
   <si>
@@ -3314,6 +3311,9 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor6665-3337-4533-b930-623330353931/-/format/webp/052e4dedcc5841e0e422929a619874a8.jpg</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor6131-6161-4131-a265-393734303231/-/format/webp/81973917.jpg</t>
   </si>
 </sst>
 </file>
@@ -3737,10 +3737,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>990</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3812,7 +3812,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -3964,7 +3964,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -3985,7 +3985,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>530</v>
@@ -3993,7 +3993,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>530</v>
@@ -4004,7 +4004,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -4116,7 +4116,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -4145,7 +4145,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>547</v>
@@ -4228,7 +4228,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -4236,7 +4236,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -4257,7 +4257,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>559</v>
@@ -4284,7 +4284,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -4540,7 +4540,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
@@ -4633,7 +4633,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>604</v>
@@ -4692,12 +4692,12 @@
         <v>113</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>611</v>
@@ -4796,7 +4796,7 @@
         <v>125</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
@@ -5020,7 +5020,7 @@
         <v>153</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>650</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
@@ -5028,7 +5028,7 @@
         <v>154</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
@@ -5036,7 +5036,7 @@
         <v>155</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
@@ -5044,7 +5044,7 @@
         <v>156</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
@@ -5052,7 +5052,7 @@
         <v>157</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
@@ -5060,7 +5060,7 @@
         <v>158</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
@@ -5068,7 +5068,7 @@
         <v>159</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
@@ -5076,7 +5076,7 @@
         <v>160</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
@@ -5084,7 +5084,7 @@
         <v>161</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
@@ -5092,7 +5092,7 @@
         <v>162</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
@@ -5100,7 +5100,7 @@
         <v>163</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
@@ -5108,7 +5108,7 @@
         <v>164</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
@@ -5116,7 +5116,7 @@
         <v>165</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
@@ -5124,7 +5124,7 @@
         <v>166</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
@@ -5132,7 +5132,7 @@
         <v>167</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
@@ -5140,7 +5140,7 @@
         <v>168</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
@@ -5148,7 +5148,7 @@
         <v>169</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
@@ -5156,7 +5156,7 @@
         <v>170</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
@@ -5164,7 +5164,7 @@
         <v>171</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
@@ -5172,7 +5172,7 @@
         <v>172</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
@@ -5180,7 +5180,7 @@
         <v>173</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
@@ -5188,7 +5188,7 @@
         <v>174</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
@@ -5196,7 +5196,7 @@
         <v>175</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
@@ -5204,7 +5204,7 @@
         <v>176</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
@@ -5212,7 +5212,7 @@
         <v>177</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
@@ -5220,7 +5220,7 @@
         <v>178</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
@@ -5228,7 +5228,7 @@
         <v>179</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
@@ -5236,7 +5236,7 @@
         <v>180</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
@@ -5244,7 +5244,7 @@
         <v>181</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
@@ -5252,7 +5252,7 @@
         <v>182</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
@@ -5260,7 +5260,7 @@
         <v>183</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
@@ -5268,15 +5268,15 @@
         <v>184</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
@@ -5284,7 +5284,7 @@
         <v>185</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
@@ -5292,7 +5292,7 @@
         <v>186</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
@@ -5300,15 +5300,15 @@
         <v>187</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
@@ -5316,7 +5316,7 @@
         <v>188</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
@@ -5324,7 +5324,7 @@
         <v>189</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
@@ -5332,7 +5332,7 @@
         <v>190</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
@@ -5340,7 +5340,7 @@
         <v>191</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
@@ -5348,7 +5348,7 @@
         <v>192</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
@@ -5356,7 +5356,7 @@
         <v>193</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
@@ -5364,7 +5364,7 @@
         <v>194</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
@@ -5372,7 +5372,7 @@
         <v>195</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
@@ -5380,7 +5380,7 @@
         <v>196</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
@@ -5388,7 +5388,7 @@
         <v>197</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
@@ -5396,7 +5396,7 @@
         <v>198</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
@@ -5404,7 +5404,7 @@
         <v>199</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
@@ -5412,7 +5412,7 @@
         <v>200</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
@@ -5420,7 +5420,7 @@
         <v>201</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
@@ -5428,7 +5428,7 @@
         <v>202</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
@@ -5436,7 +5436,7 @@
         <v>203</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
@@ -5444,7 +5444,7 @@
         <v>204</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
@@ -5452,7 +5452,7 @@
         <v>205</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
@@ -5460,7 +5460,7 @@
         <v>206</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
@@ -5468,7 +5468,7 @@
         <v>207</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
@@ -5476,7 +5476,7 @@
         <v>208</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
@@ -5484,7 +5484,7 @@
         <v>209</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
@@ -5492,7 +5492,7 @@
         <v>210</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
@@ -5500,7 +5500,7 @@
         <v>211</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
@@ -5508,7 +5508,7 @@
         <v>212</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
@@ -5516,7 +5516,7 @@
         <v>213</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
@@ -5524,7 +5524,7 @@
         <v>214</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
@@ -5532,7 +5532,7 @@
         <v>215</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
@@ -5540,7 +5540,7 @@
         <v>216</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
@@ -5548,7 +5548,7 @@
         <v>217</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
@@ -5556,7 +5556,7 @@
         <v>218</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
@@ -5564,7 +5564,7 @@
         <v>219</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
@@ -5572,7 +5572,7 @@
         <v>220</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
@@ -5580,7 +5580,7 @@
         <v>221</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
@@ -5588,7 +5588,7 @@
         <v>222</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
@@ -5596,7 +5596,7 @@
         <v>223</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
@@ -5604,7 +5604,7 @@
         <v>224</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
@@ -5612,7 +5612,7 @@
         <v>225</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
@@ -5620,7 +5620,7 @@
         <v>226</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
@@ -5628,7 +5628,7 @@
         <v>227</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
@@ -5636,7 +5636,7 @@
         <v>228</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
@@ -5644,7 +5644,7 @@
         <v>229</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
@@ -5652,7 +5652,7 @@
         <v>230</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
@@ -5660,7 +5660,7 @@
         <v>231</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
@@ -5668,7 +5668,7 @@
         <v>232</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
@@ -5676,7 +5676,7 @@
         <v>233</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
@@ -5684,7 +5684,7 @@
         <v>234</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
@@ -5692,7 +5692,7 @@
         <v>235</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
@@ -5700,7 +5700,7 @@
         <v>236</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
@@ -5708,7 +5708,7 @@
         <v>237</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
@@ -5716,7 +5716,7 @@
         <v>238</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
@@ -5724,7 +5724,7 @@
         <v>239</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
@@ -5732,7 +5732,7 @@
         <v>240</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
@@ -5740,7 +5740,7 @@
         <v>241</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
@@ -5748,7 +5748,7 @@
         <v>242</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
@@ -5756,7 +5756,7 @@
         <v>243</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
@@ -5764,7 +5764,7 @@
         <v>244</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
@@ -5772,7 +5772,7 @@
         <v>245</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
@@ -5780,7 +5780,7 @@
         <v>246</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
@@ -5788,7 +5788,7 @@
         <v>247</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
@@ -5796,7 +5796,7 @@
         <v>248</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
@@ -5804,7 +5804,7 @@
         <v>249</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
@@ -5812,7 +5812,7 @@
         <v>250</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
@@ -5820,7 +5820,7 @@
         <v>251</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
@@ -5828,7 +5828,7 @@
         <v>252</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
@@ -5836,7 +5836,7 @@
         <v>253</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
@@ -5844,7 +5844,7 @@
         <v>254</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
@@ -5852,7 +5852,7 @@
         <v>255</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
@@ -5860,7 +5860,7 @@
         <v>256</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
@@ -5868,7 +5868,7 @@
         <v>257</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
@@ -5876,7 +5876,7 @@
         <v>258</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
@@ -5884,7 +5884,7 @@
         <v>259</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
@@ -5892,7 +5892,7 @@
         <v>260</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
@@ -5900,7 +5900,7 @@
         <v>261</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
@@ -5908,7 +5908,7 @@
         <v>262</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
@@ -5916,7 +5916,7 @@
         <v>263</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
@@ -5924,7 +5924,7 @@
         <v>264</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
@@ -5932,15 +5932,15 @@
         <v>265</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
@@ -5948,7 +5948,7 @@
         <v>266</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
@@ -5956,7 +5956,7 @@
         <v>267</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
@@ -5964,7 +5964,7 @@
         <v>268</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
@@ -5972,7 +5972,7 @@
         <v>269</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
@@ -5980,7 +5980,7 @@
         <v>270</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
@@ -5988,7 +5988,7 @@
         <v>271</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
@@ -5996,7 +5996,7 @@
         <v>272</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
@@ -6004,7 +6004,7 @@
         <v>273</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
@@ -6012,7 +6012,7 @@
         <v>274</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
@@ -6020,7 +6020,7 @@
         <v>275</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
@@ -6028,7 +6028,7 @@
         <v>276</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
@@ -6036,7 +6036,7 @@
         <v>277</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
@@ -6044,7 +6044,7 @@
         <v>278</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
@@ -6052,7 +6052,7 @@
         <v>279</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
@@ -6060,7 +6060,7 @@
         <v>280</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
@@ -6068,7 +6068,7 @@
         <v>281</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
@@ -6076,7 +6076,7 @@
         <v>282</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
@@ -6084,7 +6084,7 @@
         <v>283</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
@@ -6092,7 +6092,7 @@
         <v>284</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
@@ -6100,7 +6100,7 @@
         <v>285</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
@@ -6108,7 +6108,7 @@
         <v>286</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
@@ -6116,7 +6116,7 @@
         <v>287</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
@@ -6124,7 +6124,7 @@
         <v>288</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
@@ -6132,7 +6132,7 @@
         <v>289</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
@@ -6140,7 +6140,7 @@
         <v>290</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
@@ -6148,7 +6148,7 @@
         <v>291</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
@@ -6156,7 +6156,7 @@
         <v>292</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
@@ -6164,7 +6164,7 @@
         <v>293</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
@@ -6172,7 +6172,7 @@
         <v>294</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
@@ -6180,7 +6180,7 @@
         <v>295</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
@@ -6188,7 +6188,7 @@
         <v>296</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
@@ -6196,7 +6196,7 @@
         <v>297</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
@@ -6204,7 +6204,7 @@
         <v>298</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
@@ -6212,7 +6212,7 @@
         <v>299</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
@@ -6220,7 +6220,7 @@
         <v>300</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
@@ -6228,7 +6228,7 @@
         <v>301</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
@@ -6236,7 +6236,7 @@
         <v>302</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
@@ -6244,7 +6244,7 @@
         <v>303</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
@@ -6252,7 +6252,7 @@
         <v>304</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
@@ -6260,7 +6260,7 @@
         <v>305</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
@@ -6268,7 +6268,7 @@
         <v>306</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
@@ -6276,7 +6276,7 @@
         <v>307</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
@@ -6284,7 +6284,7 @@
         <v>308</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
@@ -6292,7 +6292,7 @@
         <v>309</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
@@ -6300,7 +6300,7 @@
         <v>310</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
@@ -6308,7 +6308,7 @@
         <v>311</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
@@ -6316,7 +6316,7 @@
         <v>312</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
@@ -6332,7 +6332,7 @@
         <v>313</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
@@ -6340,7 +6340,7 @@
         <v>314</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
@@ -6348,7 +6348,7 @@
         <v>315</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
@@ -6356,7 +6356,7 @@
         <v>316</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
@@ -6364,7 +6364,7 @@
         <v>317</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
@@ -6372,7 +6372,7 @@
         <v>318</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
@@ -6380,7 +6380,7 @@
         <v>319</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
@@ -6388,7 +6388,7 @@
         <v>320</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
@@ -6396,7 +6396,7 @@
         <v>321</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
@@ -6404,7 +6404,7 @@
         <v>322</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
@@ -6412,7 +6412,7 @@
         <v>323</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
@@ -6420,7 +6420,7 @@
         <v>324</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
@@ -6428,7 +6428,7 @@
         <v>325</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
@@ -6436,7 +6436,7 @@
         <v>326</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
@@ -6444,7 +6444,7 @@
         <v>327</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
@@ -6452,7 +6452,7 @@
         <v>328</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
@@ -6460,7 +6460,7 @@
         <v>329</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
@@ -6468,7 +6468,7 @@
         <v>330</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
@@ -6476,7 +6476,7 @@
         <v>331</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
@@ -6484,7 +6484,7 @@
         <v>332</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
@@ -6492,7 +6492,7 @@
         <v>333</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
@@ -6500,7 +6500,7 @@
         <v>334</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
@@ -6508,7 +6508,7 @@
         <v>335</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
@@ -6516,7 +6516,7 @@
         <v>336</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.2">
@@ -6524,7 +6524,7 @@
         <v>337</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.2">
@@ -6532,7 +6532,7 @@
         <v>338</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
@@ -6540,7 +6540,7 @@
         <v>339</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.2">
@@ -6548,7 +6548,7 @@
         <v>340</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.2">
@@ -6556,7 +6556,7 @@
         <v>341</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.2">
@@ -6564,7 +6564,7 @@
         <v>342</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.2">
@@ -6572,7 +6572,7 @@
         <v>343</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.2">
@@ -6580,7 +6580,7 @@
         <v>344</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.2">
@@ -6588,7 +6588,7 @@
         <v>345</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.2">
@@ -6596,7 +6596,7 @@
         <v>346</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
@@ -6604,7 +6604,7 @@
         <v>347</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.2">
@@ -6612,7 +6612,7 @@
         <v>348</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.2">
@@ -6620,7 +6620,7 @@
         <v>349</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.2">
@@ -6628,7 +6628,7 @@
         <v>350</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.2">
@@ -6636,7 +6636,7 @@
         <v>351</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.2">
@@ -6644,7 +6644,7 @@
         <v>352</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.2">
@@ -6652,7 +6652,7 @@
         <v>6</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.2">
@@ -6660,7 +6660,7 @@
         <v>353</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
@@ -6668,7 +6668,7 @@
         <v>354</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.2">
@@ -6676,7 +6676,7 @@
         <v>355</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
@@ -6684,7 +6684,7 @@
         <v>356</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
@@ -6692,7 +6692,7 @@
         <v>357</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
@@ -6700,7 +6700,7 @@
         <v>358</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
@@ -6708,7 +6708,7 @@
         <v>359</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
@@ -6716,7 +6716,7 @@
         <v>360</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
@@ -6724,15 +6724,15 @@
         <v>361</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
@@ -6740,7 +6740,7 @@
         <v>362</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
@@ -6748,7 +6748,7 @@
         <v>363</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
@@ -6756,7 +6756,7 @@
         <v>364</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
@@ -6764,7 +6764,7 @@
         <v>365</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
@@ -6772,7 +6772,7 @@
         <v>366</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
@@ -6780,7 +6780,7 @@
         <v>367</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
@@ -6788,7 +6788,7 @@
         <v>368</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
@@ -6796,7 +6796,7 @@
         <v>369</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
@@ -6804,7 +6804,7 @@
         <v>370</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
@@ -6812,7 +6812,7 @@
         <v>371</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
@@ -6820,7 +6820,7 @@
         <v>372</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
@@ -6828,7 +6828,7 @@
         <v>373</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
@@ -6836,7 +6836,7 @@
         <v>374</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
@@ -6844,7 +6844,7 @@
         <v>375</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
@@ -6852,7 +6852,7 @@
         <v>376</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
@@ -6860,7 +6860,7 @@
         <v>377</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
@@ -6868,7 +6868,7 @@
         <v>378</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
@@ -6876,7 +6876,7 @@
         <v>379</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
@@ -6884,7 +6884,7 @@
         <v>380</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
@@ -6892,7 +6892,7 @@
         <v>381</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
@@ -6900,7 +6900,7 @@
         <v>382</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
@@ -6908,7 +6908,7 @@
         <v>383</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
@@ -6916,7 +6916,7 @@
         <v>384</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
@@ -6924,7 +6924,7 @@
         <v>385</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
@@ -6932,7 +6932,7 @@
         <v>386</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
@@ -6940,7 +6940,7 @@
         <v>387</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
@@ -6948,7 +6948,7 @@
         <v>388</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
@@ -6956,7 +6956,7 @@
         <v>389</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
@@ -6964,7 +6964,7 @@
         <v>390</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
@@ -6972,7 +6972,7 @@
         <v>391</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
@@ -6980,7 +6980,7 @@
         <v>392</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
@@ -6988,7 +6988,7 @@
         <v>393</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
@@ -6996,7 +6996,7 @@
         <v>394</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
@@ -7004,7 +7004,7 @@
         <v>395</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
@@ -7012,7 +7012,7 @@
         <v>396</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
@@ -7020,7 +7020,7 @@
         <v>397</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
@@ -7028,7 +7028,7 @@
         <v>398</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
@@ -7036,7 +7036,7 @@
         <v>399</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
@@ -7044,7 +7044,7 @@
         <v>400</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
@@ -7052,7 +7052,7 @@
         <v>401</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
@@ -7060,15 +7060,15 @@
         <v>402</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B417" s="2" t="s">
         <v>1022</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
@@ -7076,7 +7076,7 @@
         <v>403</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.2">
@@ -7084,7 +7084,7 @@
         <v>404</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
@@ -7092,7 +7092,7 @@
         <v>405</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.2">
@@ -7100,7 +7100,7 @@
         <v>406</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.2">
@@ -7108,7 +7108,7 @@
         <v>407</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.2">
@@ -7116,7 +7116,7 @@
         <v>408</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.2">
@@ -7124,7 +7124,7 @@
         <v>409</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
@@ -7132,7 +7132,7 @@
         <v>410</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.2">
@@ -7140,7 +7140,7 @@
         <v>411</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.2">
@@ -7148,7 +7148,7 @@
         <v>412</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
@@ -7156,7 +7156,7 @@
         <v>413</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.2">
@@ -7164,7 +7164,7 @@
         <v>414</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.2">
@@ -7172,7 +7172,7 @@
         <v>415</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.2">
@@ -7180,7 +7180,7 @@
         <v>416</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
@@ -7188,7 +7188,7 @@
         <v>417</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.2">
@@ -7196,7 +7196,7 @@
         <v>418</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.2">
@@ -7204,7 +7204,7 @@
         <v>419</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.2">
@@ -7212,7 +7212,7 @@
         <v>420</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.2">
@@ -7220,7 +7220,7 @@
         <v>421</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.2">
@@ -7228,7 +7228,7 @@
         <v>422</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.2">
@@ -7236,7 +7236,7 @@
         <v>423</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
@@ -7244,7 +7244,7 @@
         <v>424</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
@@ -7252,7 +7252,7 @@
         <v>425</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
@@ -7260,7 +7260,7 @@
         <v>426</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
@@ -7268,7 +7268,7 @@
         <v>427</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
@@ -7276,7 +7276,7 @@
         <v>428</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
@@ -7284,7 +7284,7 @@
         <v>429</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
@@ -7292,7 +7292,7 @@
         <v>430</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
@@ -7300,7 +7300,7 @@
         <v>431</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
@@ -7308,7 +7308,7 @@
         <v>432</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
@@ -7316,7 +7316,7 @@
         <v>433</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
@@ -7324,7 +7324,7 @@
         <v>434</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
@@ -7332,7 +7332,7 @@
         <v>435</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
@@ -7340,7 +7340,7 @@
         <v>436</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
@@ -7348,7 +7348,7 @@
         <v>437</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
@@ -7356,7 +7356,7 @@
         <v>438</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
@@ -7364,7 +7364,7 @@
         <v>439</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
@@ -7372,7 +7372,7 @@
         <v>440</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
@@ -7380,7 +7380,7 @@
         <v>441</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
@@ -7388,7 +7388,7 @@
         <v>442</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
@@ -7396,7 +7396,7 @@
         <v>443</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
@@ -7404,7 +7404,7 @@
         <v>444</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
@@ -7412,7 +7412,7 @@
         <v>445</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
@@ -7420,7 +7420,7 @@
         <v>446</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
@@ -7428,7 +7428,7 @@
         <v>447</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
@@ -7436,7 +7436,7 @@
         <v>448</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
@@ -7444,7 +7444,7 @@
         <v>449</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
@@ -7452,7 +7452,7 @@
         <v>450</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
@@ -7460,7 +7460,7 @@
         <v>451</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
@@ -7468,7 +7468,7 @@
         <v>452</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
@@ -7476,7 +7476,7 @@
         <v>453</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
@@ -7484,7 +7484,7 @@
         <v>454</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
@@ -7492,7 +7492,7 @@
         <v>455</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
@@ -7500,7 +7500,7 @@
         <v>456</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
@@ -7508,7 +7508,7 @@
         <v>457</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
@@ -7516,7 +7516,7 @@
         <v>458</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
@@ -7524,7 +7524,7 @@
         <v>459</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
@@ -7532,7 +7532,7 @@
         <v>460</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
@@ -7540,7 +7540,7 @@
         <v>461</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">
@@ -7548,7 +7548,7 @@
         <v>462</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
@@ -7556,7 +7556,7 @@
         <v>463</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
@@ -7564,7 +7564,7 @@
         <v>464</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
@@ -7572,7 +7572,7 @@
         <v>465</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.2">
@@ -7580,7 +7580,7 @@
         <v>466</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
@@ -7588,7 +7588,7 @@
         <v>467</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.2">
@@ -7596,15 +7596,15 @@
         <v>468</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.2">
@@ -7612,7 +7612,7 @@
         <v>469</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
@@ -7620,7 +7620,7 @@
         <v>470</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.2">
@@ -7628,7 +7628,7 @@
         <v>471</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.2">
@@ -7636,7 +7636,7 @@
         <v>472</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.2">
@@ -7644,7 +7644,7 @@
         <v>473</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.2">
@@ -7652,7 +7652,7 @@
         <v>474</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.2">
@@ -7660,7 +7660,7 @@
         <v>475</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.2">
@@ -7668,7 +7668,7 @@
         <v>476</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.2">
@@ -7676,7 +7676,7 @@
         <v>477</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.2">
@@ -7684,7 +7684,7 @@
         <v>478</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.2">
@@ -7692,7 +7692,7 @@
         <v>479</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.2">
@@ -7700,7 +7700,7 @@
         <v>480</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
@@ -7708,7 +7708,7 @@
         <v>481</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
@@ -7716,7 +7716,7 @@
         <v>482</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
@@ -7724,7 +7724,7 @@
         <v>483</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
@@ -7732,7 +7732,7 @@
         <v>484</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
@@ -7740,7 +7740,7 @@
         <v>485</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.2">
@@ -7748,7 +7748,7 @@
         <v>486</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.2">
@@ -7756,7 +7756,7 @@
         <v>487</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
@@ -7764,7 +7764,7 @@
         <v>488</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
@@ -7772,7 +7772,7 @@
         <v>489</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
@@ -7780,7 +7780,7 @@
         <v>490</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
@@ -7788,7 +7788,7 @@
         <v>491</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
@@ -7796,7 +7796,7 @@
         <v>492</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
@@ -7804,7 +7804,7 @@
         <v>493</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
@@ -7812,7 +7812,7 @@
         <v>494</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
@@ -7820,15 +7820,15 @@
         <v>495</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.2">
@@ -7836,7 +7836,7 @@
         <v>496</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.2">
@@ -7844,15 +7844,15 @@
         <v>497</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.2">
@@ -7860,7 +7860,7 @@
         <v>498</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.2">
@@ -7868,7 +7868,7 @@
         <v>499</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.2">
@@ -7876,7 +7876,7 @@
         <v>500</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.2">
@@ -7884,279 +7884,279 @@
         <v>501</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B522" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B523" t="s">
         <v>1014</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B524" t="s">
         <v>1016</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B525" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B526" t="s">
         <v>1030</v>
-      </c>
-      <c r="B526" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B527" t="s">
         <v>1032</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B528" t="s">
         <v>1035</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B529" t="s">
         <v>1041</v>
-      </c>
-      <c r="B529" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B530" t="s">
         <v>1043</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B531" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B532" t="s">
         <v>1051</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B533" t="s">
         <v>1053</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B534" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B535" t="s">
         <v>1059</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B536" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B537" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B538" t="s">
         <v>1065</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B539" t="s">
         <v>1067</v>
-      </c>
-      <c r="B539" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B540" t="s">
         <v>1069</v>
-      </c>
-      <c r="B540" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B541" t="s">
         <v>1071</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B542" t="s">
         <v>1073</v>
-      </c>
-      <c r="B542" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B543" t="s">
         <v>1075</v>
-      </c>
-      <c r="B543" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B544" t="s">
         <v>1077</v>
-      </c>
-      <c r="B544" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B545" t="s">
         <v>1079</v>
-      </c>
-      <c r="B545" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B546" t="s">
         <v>1081</v>
-      </c>
-      <c r="B546" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B547" t="s">
         <v>1083</v>
-      </c>
-      <c r="B547" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B548" t="s">
         <v>1085</v>
-      </c>
-      <c r="B548" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B549" t="s">
         <v>1087</v>
-      </c>
-      <c r="B549" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B550" t="s">
         <v>1089</v>
-      </c>
-      <c r="B550" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B551" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B552" t="s">
         <v>1093</v>
-      </c>
-      <c r="B552" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B553" t="s">
         <v>1096</v>
-      </c>
-      <c r="B553" t="s">
-        <v>1097</v>
       </c>
     </row>
   </sheetData>
@@ -8315,7 +8315,7 @@
     <hyperlink ref="B158" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
     <hyperlink ref="B159" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
     <hyperlink ref="B160" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="B161" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="B161" r:id="rId155" display="https://static.tildacdn.com/stor6566-6433-4163-b464-613937346430/58702522.jpg" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
     <hyperlink ref="B162" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
     <hyperlink ref="B163" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
     <hyperlink ref="B164" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/His.&amp;.Hers.S01.2160p.NF.WEB-DL.H.265/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F095A17B-38E7-E14F-94C7-638EA585E4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B43F645-AE1C-8E46-ABA8-C3DFFAC17C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="1102">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3314,6 +3314,18 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor6131-6161-4131-a265-393734303231/-/format/webp/81973917.jpg</t>
+  </si>
+  <si>
+    <t>PRAGMATA PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3832-3235-4434-a539-316635353963/-/format/webp/ee2c8779886a34a43c1203bd4e586f77.jpg</t>
+  </si>
+  <si>
+    <t>Crimson Desert PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3733-3562-4737-a161-623832346465/-/format/webp/b8a1f5fe58f466710926e1f20cbfba48.jpg</t>
   </si>
 </sst>
 </file>
@@ -3728,7 +3740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B553"/>
+  <dimension ref="A1:B555"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8157,6 +8169,22 @@
       </c>
       <c r="B553" t="s">
         <v>1096</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A554" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A555" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1099</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/His.&amp;.Hers.S01.2160p.NF.WEB-DL.H.265/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B43F645-AE1C-8E46-ABA8-C3DFFAC17C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849CF27F-95C8-7642-8E5F-7B8273F820E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="1102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="1104">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3326,6 +3326,12 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor3733-3562-4737-a161-623832346465/-/format/webp/b8a1f5fe58f466710926e1f20cbfba48.jpg</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor6266-3534-4036-b238-316362303334/-/format/webp/45154996.jpg</t>
+  </si>
+  <si>
+    <t>Asterix &amp; Obelix XXL3: The Crystal Menhir PS4/PS5</t>
   </si>
 </sst>
 </file>
@@ -3740,7 +3746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B555"/>
+  <dimension ref="A1:B556"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8185,6 +8191,14 @@
       </c>
       <c r="B555" t="s">
         <v>1099</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A556" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62E4047-2182-DC41-8E8B-B7E7D3FBEE70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B16CBA0-CBC6-6D49-988A-B1856CC97CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3340,10 +3340,10 @@
     <t>Life is Strange: Reunion PS5</t>
   </si>
   <si>
+    <t>https://optim.tildacdn.com/stor3637-3234-4032-b563-323538376634/-/format/webp/39079d340601e3c385d648d3c6651faa.jpg</t>
+  </si>
+  <si>
     <t>Painkiller PS5</t>
-  </si>
-  <si>
-    <t>https://optim.tildacdn.com/stor3637-3234-4032-b563-323538376634/-/format/webp/39079d340601e3c385d648d3c6651faa.jpg</t>
   </si>
 </sst>
 </file>
@@ -8223,10 +8223,10 @@
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B558" t="s">
         <v>1106</v>
-      </c>
-      <c r="B558" t="s">
-        <v>1107</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B16CBA0-CBC6-6D49-988A-B1856CC97CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DEB44F-893C-304B-81CA-B02E1DA2ADC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="27080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="1108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="1112">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -427,9 +427,6 @@
     <t>Worms WMD PS4/PS5</t>
   </si>
   <si>
-    <t>Five Nights at Freddy's: Into the Pit PS5/PS5</t>
-  </si>
-  <si>
     <t>LEGO Harry Potter Collection PS4</t>
   </si>
   <si>
@@ -3344,6 +3341,21 @@
   </si>
   <si>
     <t>Painkiller PS5</t>
+  </si>
+  <si>
+    <t>Five Nights at Freddy's: Into the Pit PS4/PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3237-6631-4432-b462-383735613034/-/format/webp/26c200ef6d6690c2e46f0d9353c53185.jpg</t>
+  </si>
+  <si>
+    <t>Starfield PS5 на Русском языке</t>
+  </si>
+  <si>
+    <t>Outer Wilds PS4/PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3963-3636-4461-b133-383466316364/-/format/webp/35822797.jpg</t>
   </si>
 </sst>
 </file>
@@ -3758,7 +3770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B558"/>
+  <dimension ref="A1:B560"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -3767,10 +3779,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>989</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3778,7 +3790,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -3786,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -3794,7 +3806,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -3802,7 +3814,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -3810,7 +3822,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -3818,7 +3830,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -3826,7 +3838,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -3834,7 +3846,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -3842,7 +3854,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -3850,7 +3862,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -3858,7 +3870,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -3866,7 +3878,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -3874,7 +3886,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -3882,7 +3894,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -3890,7 +3902,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -3898,7 +3910,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -3906,7 +3918,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -3914,7 +3926,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -3922,7 +3934,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -3930,7 +3942,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -3938,7 +3950,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -3946,7 +3958,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -3954,7 +3966,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -3962,7 +3974,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -3970,7 +3982,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -3978,7 +3990,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -3986,7 +3998,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -3994,7 +4006,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -4002,7 +4014,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -4010,23 +4022,23 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -4034,7 +4046,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -4042,7 +4054,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -4050,7 +4062,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -4058,7 +4070,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -4066,7 +4078,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -4074,7 +4086,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -4082,7 +4094,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -4090,7 +4102,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
@@ -4098,7 +4110,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
@@ -4106,7 +4118,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -4114,7 +4126,7 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
@@ -4122,7 +4134,7 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
@@ -4130,7 +4142,7 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
@@ -4138,7 +4150,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
@@ -4146,7 +4158,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -4154,7 +4166,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
@@ -4162,7 +4174,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
@@ -4170,15 +4182,15 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
@@ -4186,7 +4198,7 @@
         <v>48</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
@@ -4194,7 +4206,7 @@
         <v>49</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
@@ -4202,7 +4214,7 @@
         <v>50</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
@@ -4210,7 +4222,7 @@
         <v>51</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
@@ -4218,7 +4230,7 @@
         <v>52</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
@@ -4226,7 +4238,7 @@
         <v>53</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
@@ -4234,7 +4246,7 @@
         <v>54</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
@@ -4242,7 +4254,7 @@
         <v>55</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
@@ -4250,7 +4262,7 @@
         <v>56</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
@@ -4258,7 +4270,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -4266,7 +4278,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -4274,7 +4286,7 @@
         <v>59</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
@@ -4282,15 +4294,15 @@
         <v>60</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
@@ -4298,7 +4310,7 @@
         <v>61</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
@@ -4306,7 +4318,7 @@
         <v>62</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
@@ -4314,7 +4326,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -4322,7 +4334,7 @@
         <v>64</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
@@ -4330,7 +4342,7 @@
         <v>65</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
@@ -4338,7 +4350,7 @@
         <v>66</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
@@ -4346,7 +4358,7 @@
         <v>67</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
@@ -4354,7 +4366,7 @@
         <v>68</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
@@ -4362,7 +4374,7 @@
         <v>69</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
@@ -4370,7 +4382,7 @@
         <v>70</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
@@ -4378,7 +4390,7 @@
         <v>71</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
@@ -4386,7 +4398,7 @@
         <v>72</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
@@ -4394,7 +4406,7 @@
         <v>73</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
@@ -4402,7 +4414,7 @@
         <v>74</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
@@ -4410,7 +4422,7 @@
         <v>75</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
@@ -4418,7 +4430,7 @@
         <v>76</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
@@ -4426,7 +4438,7 @@
         <v>77</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
@@ -4434,7 +4446,7 @@
         <v>78</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
@@ -4442,7 +4454,7 @@
         <v>79</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
@@ -4450,7 +4462,7 @@
         <v>80</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
@@ -4458,7 +4470,7 @@
         <v>81</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
@@ -4466,7 +4478,7 @@
         <v>82</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
@@ -4474,7 +4486,7 @@
         <v>83</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
@@ -4482,7 +4494,7 @@
         <v>84</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
@@ -4490,7 +4502,7 @@
         <v>85</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
@@ -4498,7 +4510,7 @@
         <v>86</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
@@ -4506,7 +4518,7 @@
         <v>87</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
@@ -4514,7 +4526,7 @@
         <v>88</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
@@ -4522,7 +4534,7 @@
         <v>89</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
@@ -4530,7 +4542,7 @@
         <v>90</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
@@ -4538,7 +4550,7 @@
         <v>91</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
@@ -4546,7 +4558,7 @@
         <v>92</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
@@ -4554,7 +4566,7 @@
         <v>93</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
@@ -4562,7 +4574,7 @@
         <v>94</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
@@ -4570,7 +4582,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
@@ -4578,7 +4590,7 @@
         <v>96</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
@@ -4586,7 +4598,7 @@
         <v>97</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
@@ -4594,7 +4606,7 @@
         <v>98</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
@@ -4602,7 +4614,7 @@
         <v>99</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
@@ -4610,7 +4622,7 @@
         <v>100</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
@@ -4618,7 +4630,7 @@
         <v>101</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
@@ -4626,7 +4638,7 @@
         <v>102</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
@@ -4634,7 +4646,7 @@
         <v>103</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
@@ -4642,7 +4654,7 @@
         <v>104</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
@@ -4650,7 +4662,7 @@
         <v>105</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
@@ -4658,15 +4670,15 @@
         <v>106</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
@@ -4674,7 +4686,7 @@
         <v>107</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
@@ -4682,7 +4694,7 @@
         <v>108</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
@@ -4690,7 +4702,7 @@
         <v>109</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
@@ -4698,7 +4710,7 @@
         <v>110</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
@@ -4706,7 +4718,7 @@
         <v>111</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
@@ -4714,7 +4726,7 @@
         <v>112</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
@@ -4722,15 +4734,15 @@
         <v>113</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
@@ -4738,7 +4750,7 @@
         <v>114</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
@@ -4746,7 +4758,7 @@
         <v>115</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
@@ -4754,7 +4766,7 @@
         <v>116</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
@@ -4762,7 +4774,7 @@
         <v>117</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
@@ -4770,7 +4782,7 @@
         <v>118</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
@@ -4778,7 +4790,7 @@
         <v>119</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
@@ -4786,7 +4798,7 @@
         <v>120</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
@@ -4794,7 +4806,7 @@
         <v>121</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
@@ -4802,7 +4814,7 @@
         <v>122</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
@@ -4810,7 +4822,7 @@
         <v>123</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
@@ -4818,7 +4830,7 @@
         <v>124</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
@@ -4826,7 +4838,7 @@
         <v>125</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
@@ -4834,7 +4846,7 @@
         <v>126</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
@@ -4842,7 +4854,7 @@
         <v>127</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
@@ -4850,7 +4862,7 @@
         <v>128</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
@@ -4858,7 +4870,7 @@
         <v>129</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
@@ -4866,7 +4878,7 @@
         <v>130</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
@@ -4874,7 +4886,7 @@
         <v>131</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
@@ -4882,7 +4894,7 @@
         <v>132</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
@@ -4890,7 +4902,7 @@
         <v>133</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
@@ -4898,1455 +4910,1455 @@
         <v>134</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>135</v>
+        <v>1107</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
@@ -6354,327 +6366,327 @@
         <v>45</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.2">
@@ -6682,1551 +6694,1567 @@
         <v>6</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B417" s="2" t="s">
         <v>1021</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B522" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B523" t="s">
         <v>1013</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B524" t="s">
         <v>1015</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B525" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B526" t="s">
         <v>1029</v>
-      </c>
-      <c r="B526" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B527" t="s">
         <v>1031</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B528" t="s">
         <v>1034</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B529" t="s">
         <v>1040</v>
-      </c>
-      <c r="B529" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B530" t="s">
         <v>1042</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B531" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B532" t="s">
         <v>1050</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B533" t="s">
         <v>1052</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B534" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B535" t="s">
         <v>1058</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B536" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B537" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B538" t="s">
         <v>1064</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B539" t="s">
         <v>1066</v>
-      </c>
-      <c r="B539" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B540" t="s">
         <v>1068</v>
-      </c>
-      <c r="B540" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B541" t="s">
         <v>1070</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B542" t="s">
         <v>1072</v>
-      </c>
-      <c r="B542" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B543" t="s">
         <v>1074</v>
-      </c>
-      <c r="B543" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B544" t="s">
         <v>1076</v>
-      </c>
-      <c r="B544" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B545" t="s">
         <v>1078</v>
-      </c>
-      <c r="B545" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B546" t="s">
         <v>1080</v>
-      </c>
-      <c r="B546" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B547" t="s">
         <v>1082</v>
-      </c>
-      <c r="B547" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B548" t="s">
         <v>1084</v>
-      </c>
-      <c r="B548" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B549" t="s">
         <v>1086</v>
-      </c>
-      <c r="B549" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B550" t="s">
         <v>1088</v>
-      </c>
-      <c r="B550" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B551" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B552" t="s">
         <v>1092</v>
-      </c>
-      <c r="B552" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B553" t="s">
         <v>1095</v>
-      </c>
-      <c r="B553" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B554" t="s">
         <v>1100</v>
-      </c>
-      <c r="B554" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B555" t="s">
         <v>1098</v>
-      </c>
-      <c r="B555" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B556" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B557" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B558" t="s">
-        <v>1106</v>
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A559" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A560" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1111</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DEB44F-893C-304B-81CA-B02E1DA2ADC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13489C7F-EB99-C042-9372-F1A06BA8FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="27080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="1112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="1116">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -2797,9 +2797,6 @@
     <t>https://static.tildacdn.com/stor6334-3938-4330-b635-323732633132/26864190.jpg</t>
   </si>
   <si>
-    <t>https://static.tildacdn.com/stor3662-6639-4733-b130-386162623738/80643264.jpg</t>
-  </si>
-  <si>
     <t>https://static.tildacdn.com/stor3365-6463-4237-b933-383234326232/71661497.jpg</t>
   </si>
   <si>
@@ -3356,6 +3353,21 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor3963-3636-4461-b133-383466316364/-/format/webp/35822797.jpg</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3637-3866-4433-b130-343739626565/-/format/webp/18249a29b35708e9d561a162e6a5ec1a.png</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor6235-3862-4133-b431-323130663637/-/format/webp/6fd1f1b6fca19184cd6f8069a8336408.jpg</t>
+  </si>
+  <si>
+    <t>Hades 2 PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor6466-6561-4130-a637-306435393538/-/format/webp/336db8ffc6854500bdfae8b82f0f3c20.jpg</t>
+  </si>
+  <si>
+    <t>MOUSE: P.I. For Hire PS5</t>
   </si>
 </sst>
 </file>
@@ -3770,7 +3782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B560"/>
+  <dimension ref="A1:B562"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -3779,10 +3791,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>988</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3854,7 +3866,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -4006,7 +4018,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -4027,7 +4039,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>529</v>
@@ -4035,7 +4047,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>529</v>
@@ -4046,7 +4058,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -4158,7 +4170,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -4187,7 +4199,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>546</v>
@@ -4270,7 +4282,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -4278,7 +4290,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -4299,7 +4311,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>558</v>
@@ -4326,7 +4338,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -4582,7 +4594,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
@@ -4675,7 +4687,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>603</v>
@@ -4734,12 +4746,12 @@
         <v>113</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>610</v>
@@ -4838,7 +4850,7 @@
         <v>125</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
@@ -4915,7 +4927,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>631</v>
@@ -5062,7 +5074,7 @@
         <v>152</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
@@ -5262,7 +5274,7 @@
         <v>177</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
@@ -5278,7 +5290,7 @@
         <v>179</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
@@ -5315,7 +5327,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>678</v>
@@ -5334,7 +5346,7 @@
         <v>185</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
@@ -5347,7 +5359,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>681</v>
@@ -5446,7 +5458,7 @@
         <v>198</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
@@ -5470,7 +5482,7 @@
         <v>201</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
@@ -5494,7 +5506,7 @@
         <v>204</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
@@ -5558,7 +5570,7 @@
         <v>212</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
@@ -5774,7 +5786,7 @@
         <v>239</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
@@ -5979,7 +5991,7 @@
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>755</v>
@@ -6766,12 +6778,12 @@
         <v>360</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>852</v>
@@ -6830,7 +6842,7 @@
         <v>367</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
@@ -6926,7 +6938,7 @@
         <v>379</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
@@ -7062,7 +7074,7 @@
         <v>396</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
@@ -7107,10 +7119,10 @@
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B417" s="2" t="s">
         <v>1020</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
@@ -7126,7 +7138,7 @@
         <v>403</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
@@ -7302,7 +7314,7 @@
         <v>425</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
@@ -7406,7 +7418,7 @@
         <v>438</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>925</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
@@ -7414,7 +7426,7 @@
         <v>439</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
@@ -7422,7 +7434,7 @@
         <v>440</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
@@ -7430,7 +7442,7 @@
         <v>441</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
@@ -7438,7 +7450,7 @@
         <v>442</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
@@ -7446,7 +7458,7 @@
         <v>443</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
@@ -7454,7 +7466,7 @@
         <v>444</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
@@ -7462,7 +7474,7 @@
         <v>445</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
@@ -7470,7 +7482,7 @@
         <v>446</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
@@ -7478,7 +7490,7 @@
         <v>447</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
@@ -7486,7 +7498,7 @@
         <v>448</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
@@ -7494,7 +7506,7 @@
         <v>449</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
@@ -7502,7 +7514,7 @@
         <v>450</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
@@ -7510,7 +7522,7 @@
         <v>451</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
@@ -7518,7 +7530,7 @@
         <v>452</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
@@ -7526,7 +7538,7 @@
         <v>453</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
@@ -7534,7 +7546,7 @@
         <v>454</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
@@ -7542,7 +7554,7 @@
         <v>455</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
@@ -7550,7 +7562,7 @@
         <v>456</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
@@ -7558,7 +7570,7 @@
         <v>457</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
@@ -7566,7 +7578,7 @@
         <v>458</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
@@ -7574,7 +7586,7 @@
         <v>459</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
@@ -7582,7 +7594,7 @@
         <v>460</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">
@@ -7590,7 +7602,7 @@
         <v>461</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
@@ -7598,7 +7610,7 @@
         <v>462</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
@@ -7606,7 +7618,7 @@
         <v>463</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
@@ -7614,7 +7626,7 @@
         <v>464</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.2">
@@ -7622,7 +7634,7 @@
         <v>465</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
@@ -7630,7 +7642,7 @@
         <v>466</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.2">
@@ -7638,15 +7650,15 @@
         <v>467</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.2">
@@ -7654,7 +7666,7 @@
         <v>468</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
@@ -7662,7 +7674,7 @@
         <v>469</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.2">
@@ -7670,7 +7682,7 @@
         <v>470</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.2">
@@ -7678,7 +7690,7 @@
         <v>471</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.2">
@@ -7686,7 +7698,7 @@
         <v>472</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.2">
@@ -7694,7 +7706,7 @@
         <v>473</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.2">
@@ -7702,7 +7714,7 @@
         <v>474</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.2">
@@ -7710,7 +7722,7 @@
         <v>475</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.2">
@@ -7718,7 +7730,7 @@
         <v>476</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.2">
@@ -7726,7 +7738,7 @@
         <v>477</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.2">
@@ -7734,7 +7746,7 @@
         <v>478</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.2">
@@ -7742,7 +7754,7 @@
         <v>479</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
@@ -7750,7 +7762,7 @@
         <v>480</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
@@ -7758,7 +7770,7 @@
         <v>481</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
@@ -7766,7 +7778,7 @@
         <v>482</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
@@ -7774,7 +7786,7 @@
         <v>483</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
@@ -7782,7 +7794,7 @@
         <v>484</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.2">
@@ -7790,7 +7802,7 @@
         <v>485</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.2">
@@ -7798,7 +7810,7 @@
         <v>486</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
@@ -7806,7 +7818,7 @@
         <v>487</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
@@ -7814,7 +7826,7 @@
         <v>488</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
@@ -7822,7 +7834,7 @@
         <v>489</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
@@ -7830,7 +7842,7 @@
         <v>490</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
@@ -7838,7 +7850,7 @@
         <v>491</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
@@ -7846,7 +7858,7 @@
         <v>492</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
@@ -7854,7 +7866,7 @@
         <v>493</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
@@ -7862,15 +7874,15 @@
         <v>494</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.2">
@@ -7878,7 +7890,7 @@
         <v>495</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.2">
@@ -7886,15 +7898,15 @@
         <v>496</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.2">
@@ -7902,7 +7914,7 @@
         <v>497</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.2">
@@ -7910,7 +7922,7 @@
         <v>498</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.2">
@@ -7918,7 +7930,7 @@
         <v>499</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.2">
@@ -7926,335 +7938,351 @@
         <v>500</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B522" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B523" t="s">
         <v>1012</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B524" t="s">
         <v>1014</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B525" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B526" t="s">
         <v>1028</v>
-      </c>
-      <c r="B526" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B527" t="s">
         <v>1030</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B528" t="s">
         <v>1033</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B529" t="s">
         <v>1039</v>
-      </c>
-      <c r="B529" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B530" t="s">
         <v>1041</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B531" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B532" t="s">
         <v>1049</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B533" t="s">
         <v>1051</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B534" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B535" t="s">
         <v>1057</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B536" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B537" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B538" t="s">
         <v>1063</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B539" t="s">
         <v>1065</v>
-      </c>
-      <c r="B539" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B540" t="s">
         <v>1067</v>
-      </c>
-      <c r="B540" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B541" t="s">
         <v>1069</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B542" t="s">
         <v>1071</v>
-      </c>
-      <c r="B542" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B543" t="s">
         <v>1073</v>
-      </c>
-      <c r="B543" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B544" t="s">
         <v>1075</v>
-      </c>
-      <c r="B544" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B545" t="s">
         <v>1077</v>
-      </c>
-      <c r="B545" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B546" t="s">
         <v>1079</v>
-      </c>
-      <c r="B546" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B547" t="s">
         <v>1081</v>
-      </c>
-      <c r="B547" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B548" t="s">
         <v>1083</v>
-      </c>
-      <c r="B548" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B549" t="s">
         <v>1085</v>
-      </c>
-      <c r="B549" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B550" t="s">
         <v>1087</v>
-      </c>
-      <c r="B550" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B551" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B552" t="s">
         <v>1091</v>
-      </c>
-      <c r="B552" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B553" t="s">
         <v>1094</v>
-      </c>
-      <c r="B553" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B554" t="s">
         <v>1099</v>
-      </c>
-      <c r="B554" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B555" t="s">
         <v>1097</v>
-      </c>
-      <c r="B555" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B556" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B557" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B558" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B559" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B560" t="s">
         <v>1110</v>
       </c>
-      <c r="B560" t="s">
-        <v>1111</v>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A561" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A562" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1114</v>
       </c>
     </row>
   </sheetData>
@@ -8703,7 +8731,7 @@
     <hyperlink ref="B451" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
     <hyperlink ref="B452" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
     <hyperlink ref="B453" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="B454" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="B454" r:id="rId445" display="https://static.tildacdn.com/stor3662-6639-4733-b130-386162623738/80643264.jpg" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
     <hyperlink ref="B455" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
     <hyperlink ref="B456" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
     <hyperlink ref="B457" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13489C7F-EB99-C042-9372-F1A06BA8FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E64A0E1-93B0-164F-B706-9701F4329A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="27080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="1118">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3368,6 +3368,12 @@
   </si>
   <si>
     <t>MOUSE: P.I. For Hire PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3366-6330-4634-b461-343935313264/-/format/webp/e19a7561a97a06d7488ffed20d68d174.jpg</t>
+  </si>
+  <si>
+    <t>Atomic Heart - Blood On Crystal PS4/PS5</t>
   </si>
 </sst>
 </file>
@@ -3782,7 +3788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B562"/>
+  <dimension ref="A1:B563"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8283,6 +8289,14 @@
       </c>
       <c r="B562" t="s">
         <v>1114</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A563" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1116</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E64A0E1-93B0-164F-B706-9701F4329A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AE3C61-6B91-804B-B93A-84D3DE37D39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="27080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="1118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="1120">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3374,6 +3374,12 @@
   </si>
   <si>
     <t>Atomic Heart - Blood On Crystal PS4/PS5</t>
+  </si>
+  <si>
+    <t>007 First Light PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor6236-6536-4138-a538-323439333535/-/format/webp/67ebf378701e2ba303492d5add0fc3f8.jpg</t>
   </si>
 </sst>
 </file>
@@ -3788,7 +3794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B563"/>
+  <dimension ref="A1:B564"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8297,6 +8303,14 @@
       </c>
       <c r="B563" t="s">
         <v>1116</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A564" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1119</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AE3C61-6B91-804B-B93A-84D3DE37D39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B87B063-4669-D94F-84EA-8F79A170D09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="1122">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3380,6 +3380,12 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor6236-6536-4138-a538-323439333535/-/format/webp/67ebf378701e2ba303492d5add0fc3f8.jpg</t>
+  </si>
+  <si>
+    <t>From The Ashes Expansion DLC Avatar: Frontiers of Pandora PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3736-3234-4163-b331-323862316664/-/format/webp/a7f1181322dc1818c7b0999b69f8fcc1.jpg</t>
   </si>
 </sst>
 </file>
@@ -3794,7 +3800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B564"/>
+  <dimension ref="A1:B565"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8311,6 +8317,14 @@
       </c>
       <c r="B564" t="s">
         <v>1119</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A565" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1121</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B87B063-4669-D94F-84EA-8F79A170D09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11687D0A-A60C-F94F-B6C6-380142E8581C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="16900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="1124">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3386,6 +3386,12 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor3736-3234-4163-b331-323862316664/-/format/webp/a7f1181322dc1818c7b0999b69f8fcc1.jpg</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3233-3632-4631-b636-633363663133/-/format/webp/507ec3b558918079c280298b77fb1c17.jpg</t>
+  </si>
+  <si>
+    <t>SAROS PS5</t>
   </si>
 </sst>
 </file>
@@ -3800,7 +3806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B565"/>
+  <dimension ref="A1:B566"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8325,6 +8331,14 @@
       </c>
       <c r="B565" t="s">
         <v>1121</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A566" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1122</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11687D0A-A60C-F94F-B6C6-380142E8581C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D98CC3D-85FB-904F-AFDE-B44682136C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="16900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -844,9 +844,6 @@
     <t>Nioh Collection PS4/PS5 Remastered</t>
   </si>
   <si>
-    <t>No Man’s Sky PS4/PS5</t>
-  </si>
-  <si>
     <t>Nobody wants to DIE PS5</t>
   </si>
   <si>
@@ -3392,6 +3389,9 @@
   </si>
   <si>
     <t>SAROS PS5</t>
+  </si>
+  <si>
+    <t>No Mans Sky PS4/PS5</t>
   </si>
 </sst>
 </file>
@@ -3815,10 +3815,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>987</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -3834,7 +3834,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -3842,7 +3842,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -3850,7 +3850,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -3858,7 +3858,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -3866,7 +3866,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -3874,7 +3874,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -3882,7 +3882,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -3890,7 +3890,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -3898,7 +3898,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -3906,7 +3906,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -3914,7 +3914,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -3922,7 +3922,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -3930,7 +3930,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -3938,7 +3938,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -3946,7 +3946,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -3954,7 +3954,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -3962,7 +3962,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -3970,7 +3970,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -3978,7 +3978,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -3986,7 +3986,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -3994,7 +3994,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -4002,7 +4002,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -4010,7 +4010,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -4018,7 +4018,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -4026,7 +4026,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -4034,7 +4034,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -4042,7 +4042,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -4050,7 +4050,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -4058,23 +4058,23 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -4082,7 +4082,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -4090,7 +4090,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -4098,7 +4098,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -4106,7 +4106,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -4114,7 +4114,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -4122,7 +4122,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -4130,7 +4130,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -4138,7 +4138,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
@@ -4146,7 +4146,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
@@ -4154,7 +4154,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -4162,7 +4162,7 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
@@ -4170,7 +4170,7 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
@@ -4178,7 +4178,7 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
@@ -4186,7 +4186,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
@@ -4194,7 +4194,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -4202,7 +4202,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
@@ -4210,7 +4210,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
@@ -4218,15 +4218,15 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
@@ -4234,7 +4234,7 @@
         <v>48</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
@@ -4242,7 +4242,7 @@
         <v>49</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
@@ -4250,7 +4250,7 @@
         <v>50</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
@@ -4258,7 +4258,7 @@
         <v>51</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
@@ -4266,7 +4266,7 @@
         <v>52</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
@@ -4274,7 +4274,7 @@
         <v>53</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
@@ -4282,7 +4282,7 @@
         <v>54</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
@@ -4290,7 +4290,7 @@
         <v>55</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
@@ -4298,7 +4298,7 @@
         <v>56</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
@@ -4306,7 +4306,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -4314,7 +4314,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -4322,7 +4322,7 @@
         <v>59</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
@@ -4330,15 +4330,15 @@
         <v>60</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
@@ -4346,7 +4346,7 @@
         <v>61</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
@@ -4354,7 +4354,7 @@
         <v>62</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
@@ -4362,7 +4362,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -4370,7 +4370,7 @@
         <v>64</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
@@ -4378,7 +4378,7 @@
         <v>65</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
@@ -4386,7 +4386,7 @@
         <v>66</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
@@ -4394,7 +4394,7 @@
         <v>67</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
@@ -4402,7 +4402,7 @@
         <v>68</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
@@ -4410,7 +4410,7 @@
         <v>69</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
@@ -4418,7 +4418,7 @@
         <v>70</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
@@ -4426,7 +4426,7 @@
         <v>71</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
@@ -4434,7 +4434,7 @@
         <v>72</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
@@ -4442,7 +4442,7 @@
         <v>73</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
@@ -4450,7 +4450,7 @@
         <v>74</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
@@ -4458,7 +4458,7 @@
         <v>75</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
@@ -4466,7 +4466,7 @@
         <v>76</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
@@ -4474,7 +4474,7 @@
         <v>77</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
@@ -4482,7 +4482,7 @@
         <v>78</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
@@ -4490,7 +4490,7 @@
         <v>79</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
@@ -4498,7 +4498,7 @@
         <v>80</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
@@ -4506,7 +4506,7 @@
         <v>81</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
@@ -4514,7 +4514,7 @@
         <v>82</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
@@ -4522,7 +4522,7 @@
         <v>83</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
@@ -4530,7 +4530,7 @@
         <v>84</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
@@ -4538,7 +4538,7 @@
         <v>85</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
@@ -4546,7 +4546,7 @@
         <v>86</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
@@ -4554,7 +4554,7 @@
         <v>87</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
@@ -4562,7 +4562,7 @@
         <v>88</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
@@ -4570,7 +4570,7 @@
         <v>89</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
@@ -4578,7 +4578,7 @@
         <v>90</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
@@ -4586,7 +4586,7 @@
         <v>91</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
@@ -4594,7 +4594,7 @@
         <v>92</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
@@ -4602,7 +4602,7 @@
         <v>93</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
@@ -4610,7 +4610,7 @@
         <v>94</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
@@ -4618,7 +4618,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
@@ -4626,7 +4626,7 @@
         <v>96</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
@@ -4634,7 +4634,7 @@
         <v>97</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
@@ -4642,7 +4642,7 @@
         <v>98</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
@@ -4650,7 +4650,7 @@
         <v>99</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
@@ -4658,7 +4658,7 @@
         <v>100</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
@@ -4666,7 +4666,7 @@
         <v>101</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
@@ -4674,7 +4674,7 @@
         <v>102</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
@@ -4682,7 +4682,7 @@
         <v>103</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
@@ -4690,7 +4690,7 @@
         <v>104</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
@@ -4698,7 +4698,7 @@
         <v>105</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
@@ -4706,15 +4706,15 @@
         <v>106</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
@@ -4722,7 +4722,7 @@
         <v>107</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
@@ -4730,7 +4730,7 @@
         <v>108</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
@@ -4738,7 +4738,7 @@
         <v>109</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
@@ -4746,7 +4746,7 @@
         <v>110</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
@@ -4754,7 +4754,7 @@
         <v>111</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
@@ -4762,7 +4762,7 @@
         <v>112</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
@@ -4770,15 +4770,15 @@
         <v>113</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
@@ -4786,7 +4786,7 @@
         <v>114</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
@@ -4794,7 +4794,7 @@
         <v>115</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
@@ -4802,7 +4802,7 @@
         <v>116</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
@@ -4810,7 +4810,7 @@
         <v>117</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
@@ -4818,7 +4818,7 @@
         <v>118</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
@@ -4826,7 +4826,7 @@
         <v>119</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
@@ -4834,7 +4834,7 @@
         <v>120</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
@@ -4842,7 +4842,7 @@
         <v>121</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
@@ -4850,7 +4850,7 @@
         <v>122</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
@@ -4858,7 +4858,7 @@
         <v>123</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
@@ -4866,7 +4866,7 @@
         <v>124</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
@@ -4874,7 +4874,7 @@
         <v>125</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
@@ -4882,7 +4882,7 @@
         <v>126</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
@@ -4890,7 +4890,7 @@
         <v>127</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
@@ -4898,7 +4898,7 @@
         <v>128</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
@@ -4906,7 +4906,7 @@
         <v>129</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
@@ -4914,7 +4914,7 @@
         <v>130</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
@@ -4922,7 +4922,7 @@
         <v>131</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
@@ -4930,7 +4930,7 @@
         <v>132</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
@@ -4938,7 +4938,7 @@
         <v>133</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
@@ -4946,15 +4946,15 @@
         <v>134</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
@@ -4962,7 +4962,7 @@
         <v>135</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
@@ -4970,7 +4970,7 @@
         <v>136</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
@@ -4978,7 +4978,7 @@
         <v>137</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
@@ -4986,7 +4986,7 @@
         <v>138</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
@@ -4994,7 +4994,7 @@
         <v>139</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
@@ -5002,7 +5002,7 @@
         <v>140</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
@@ -5010,7 +5010,7 @@
         <v>141</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
@@ -5018,7 +5018,7 @@
         <v>142</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
@@ -5026,7 +5026,7 @@
         <v>143</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
@@ -5034,7 +5034,7 @@
         <v>144</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
@@ -5042,7 +5042,7 @@
         <v>145</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
@@ -5050,7 +5050,7 @@
         <v>146</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
@@ -5058,7 +5058,7 @@
         <v>147</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
@@ -5066,7 +5066,7 @@
         <v>148</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
@@ -5074,7 +5074,7 @@
         <v>149</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
@@ -5082,7 +5082,7 @@
         <v>150</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
@@ -5090,7 +5090,7 @@
         <v>151</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
@@ -5098,7 +5098,7 @@
         <v>152</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
@@ -5106,7 +5106,7 @@
         <v>153</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
@@ -5114,7 +5114,7 @@
         <v>154</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
@@ -5122,7 +5122,7 @@
         <v>155</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
@@ -5130,7 +5130,7 @@
         <v>156</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
@@ -5138,7 +5138,7 @@
         <v>157</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
@@ -5146,7 +5146,7 @@
         <v>158</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
@@ -5154,7 +5154,7 @@
         <v>159</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
@@ -5162,7 +5162,7 @@
         <v>160</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
@@ -5170,7 +5170,7 @@
         <v>161</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
@@ -5178,7 +5178,7 @@
         <v>162</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
@@ -5186,7 +5186,7 @@
         <v>163</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
@@ -5194,7 +5194,7 @@
         <v>164</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
@@ -5202,7 +5202,7 @@
         <v>165</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
@@ -5210,7 +5210,7 @@
         <v>166</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
@@ -5218,7 +5218,7 @@
         <v>167</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
@@ -5226,7 +5226,7 @@
         <v>168</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
@@ -5234,7 +5234,7 @@
         <v>169</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
@@ -5242,7 +5242,7 @@
         <v>170</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
@@ -5250,7 +5250,7 @@
         <v>171</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
@@ -5258,7 +5258,7 @@
         <v>172</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
@@ -5266,7 +5266,7 @@
         <v>173</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
@@ -5274,7 +5274,7 @@
         <v>174</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
@@ -5282,7 +5282,7 @@
         <v>175</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
@@ -5290,7 +5290,7 @@
         <v>176</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
@@ -5298,7 +5298,7 @@
         <v>177</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
@@ -5306,7 +5306,7 @@
         <v>178</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
@@ -5314,7 +5314,7 @@
         <v>179</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
@@ -5322,7 +5322,7 @@
         <v>180</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
@@ -5330,7 +5330,7 @@
         <v>181</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
@@ -5338,7 +5338,7 @@
         <v>182</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
@@ -5346,15 +5346,15 @@
         <v>183</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
@@ -5362,7 +5362,7 @@
         <v>184</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
@@ -5370,7 +5370,7 @@
         <v>185</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
@@ -5378,15 +5378,15 @@
         <v>186</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
@@ -5394,7 +5394,7 @@
         <v>187</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
@@ -5402,7 +5402,7 @@
         <v>188</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
@@ -5410,7 +5410,7 @@
         <v>189</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
@@ -5418,7 +5418,7 @@
         <v>190</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
@@ -5426,7 +5426,7 @@
         <v>191</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
@@ -5434,7 +5434,7 @@
         <v>192</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
@@ -5442,7 +5442,7 @@
         <v>193</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
@@ -5450,7 +5450,7 @@
         <v>194</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
@@ -5458,7 +5458,7 @@
         <v>195</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
@@ -5466,7 +5466,7 @@
         <v>196</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
@@ -5474,7 +5474,7 @@
         <v>197</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
@@ -5482,7 +5482,7 @@
         <v>198</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
@@ -5490,7 +5490,7 @@
         <v>199</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
@@ -5498,7 +5498,7 @@
         <v>200</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
@@ -5506,7 +5506,7 @@
         <v>201</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
@@ -5514,7 +5514,7 @@
         <v>202</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
@@ -5522,7 +5522,7 @@
         <v>203</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
@@ -5530,7 +5530,7 @@
         <v>204</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
@@ -5538,7 +5538,7 @@
         <v>205</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
@@ -5546,7 +5546,7 @@
         <v>206</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
@@ -5554,7 +5554,7 @@
         <v>207</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
@@ -5562,7 +5562,7 @@
         <v>208</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
@@ -5570,7 +5570,7 @@
         <v>209</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
@@ -5578,7 +5578,7 @@
         <v>210</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
@@ -5586,7 +5586,7 @@
         <v>211</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
@@ -5594,7 +5594,7 @@
         <v>212</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
@@ -5602,7 +5602,7 @@
         <v>213</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
@@ -5610,7 +5610,7 @@
         <v>214</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
@@ -5618,7 +5618,7 @@
         <v>215</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
@@ -5626,7 +5626,7 @@
         <v>216</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
@@ -5634,7 +5634,7 @@
         <v>217</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
@@ -5642,7 +5642,7 @@
         <v>218</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
@@ -5650,7 +5650,7 @@
         <v>219</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
@@ -5658,7 +5658,7 @@
         <v>220</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
@@ -5666,7 +5666,7 @@
         <v>221</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
@@ -5674,7 +5674,7 @@
         <v>222</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
@@ -5682,7 +5682,7 @@
         <v>223</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
@@ -5690,7 +5690,7 @@
         <v>224</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
@@ -5698,7 +5698,7 @@
         <v>225</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
@@ -5706,7 +5706,7 @@
         <v>226</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
@@ -5714,7 +5714,7 @@
         <v>227</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
@@ -5722,7 +5722,7 @@
         <v>228</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
@@ -5730,7 +5730,7 @@
         <v>229</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
@@ -5738,7 +5738,7 @@
         <v>230</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
@@ -5746,7 +5746,7 @@
         <v>231</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
@@ -5754,7 +5754,7 @@
         <v>232</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
@@ -5762,7 +5762,7 @@
         <v>233</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
@@ -5770,7 +5770,7 @@
         <v>234</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
@@ -5778,7 +5778,7 @@
         <v>235</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
@@ -5786,7 +5786,7 @@
         <v>236</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
@@ -5794,7 +5794,7 @@
         <v>237</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
@@ -5802,7 +5802,7 @@
         <v>238</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
@@ -5810,7 +5810,7 @@
         <v>239</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
@@ -5818,7 +5818,7 @@
         <v>240</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
@@ -5826,7 +5826,7 @@
         <v>241</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
@@ -5834,7 +5834,7 @@
         <v>242</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
@@ -5842,7 +5842,7 @@
         <v>243</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
@@ -5850,7 +5850,7 @@
         <v>244</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
@@ -5858,7 +5858,7 @@
         <v>245</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
@@ -5866,7 +5866,7 @@
         <v>246</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
@@ -5874,7 +5874,7 @@
         <v>247</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
@@ -5882,7 +5882,7 @@
         <v>248</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
@@ -5890,7 +5890,7 @@
         <v>249</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
@@ -5898,7 +5898,7 @@
         <v>250</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
@@ -5906,7 +5906,7 @@
         <v>251</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
@@ -5914,7 +5914,7 @@
         <v>252</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
@@ -5922,7 +5922,7 @@
         <v>253</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
@@ -5930,7 +5930,7 @@
         <v>254</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
@@ -5938,7 +5938,7 @@
         <v>255</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
@@ -5946,7 +5946,7 @@
         <v>256</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
@@ -5954,7 +5954,7 @@
         <v>257</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
@@ -5962,7 +5962,7 @@
         <v>258</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
@@ -5970,7 +5970,7 @@
         <v>259</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
@@ -5978,7 +5978,7 @@
         <v>260</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
@@ -5986,7 +5986,7 @@
         <v>261</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
@@ -5994,7 +5994,7 @@
         <v>262</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
@@ -6002,7 +6002,7 @@
         <v>263</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
@@ -6010,15 +6010,15 @@
         <v>264</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
@@ -6026,7 +6026,7 @@
         <v>265</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
@@ -6034,7 +6034,7 @@
         <v>266</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
@@ -6042,7 +6042,7 @@
         <v>267</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
@@ -6050,7 +6050,7 @@
         <v>268</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
@@ -6058,7 +6058,7 @@
         <v>269</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
@@ -6066,7 +6066,7 @@
         <v>270</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
@@ -6074,7 +6074,7 @@
         <v>271</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
@@ -6082,7 +6082,7 @@
         <v>272</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
@@ -6090,311 +6090,311 @@
         <v>273</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>274</v>
+        <v>1123</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
@@ -6402,327 +6402,327 @@
         <v>45</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.2">
@@ -6730,1615 +6730,1615 @@
         <v>6</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B417" s="2" t="s">
         <v>1019</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B522" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B523" t="s">
         <v>1011</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B524" t="s">
         <v>1013</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B525" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B526" t="s">
         <v>1027</v>
-      </c>
-      <c r="B526" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B527" t="s">
         <v>1029</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B528" t="s">
         <v>1032</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B529" t="s">
         <v>1038</v>
-      </c>
-      <c r="B529" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B530" t="s">
         <v>1040</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B531" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B532" t="s">
         <v>1048</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B533" t="s">
         <v>1050</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B534" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B535" t="s">
         <v>1056</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B536" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B537" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B538" t="s">
         <v>1062</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B539" t="s">
         <v>1064</v>
-      </c>
-      <c r="B539" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B540" t="s">
         <v>1066</v>
-      </c>
-      <c r="B540" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B541" t="s">
         <v>1068</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B542" t="s">
         <v>1070</v>
-      </c>
-      <c r="B542" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B543" t="s">
         <v>1072</v>
-      </c>
-      <c r="B543" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B544" t="s">
         <v>1074</v>
-      </c>
-      <c r="B544" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B545" t="s">
         <v>1076</v>
-      </c>
-      <c r="B545" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B546" t="s">
         <v>1078</v>
-      </c>
-      <c r="B546" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B547" t="s">
         <v>1080</v>
-      </c>
-      <c r="B547" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B548" t="s">
         <v>1082</v>
-      </c>
-      <c r="B548" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B549" t="s">
         <v>1084</v>
-      </c>
-      <c r="B549" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B550" t="s">
         <v>1086</v>
-      </c>
-      <c r="B550" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B551" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B552" t="s">
         <v>1090</v>
-      </c>
-      <c r="B552" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B553" t="s">
         <v>1093</v>
-      </c>
-      <c r="B553" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B554" t="s">
         <v>1098</v>
-      </c>
-      <c r="B554" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B555" t="s">
         <v>1096</v>
-      </c>
-      <c r="B555" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B556" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B557" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B558" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B559" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B560" t="s">
         <v>1109</v>
-      </c>
-      <c r="B560" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B561" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B562" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B563" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B564" t="s">
         <v>1118</v>
-      </c>
-      <c r="B564" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B565" t="s">
         <v>1120</v>
-      </c>
-      <c r="B565" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B566" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D98CC3D-85FB-904F-AFDE-B44682136C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489CDAD2-FB32-784D-A02F-8C812E747A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2314,9 +2314,6 @@
     <t>https://static.tildacdn.com/stor3863-3134-4363-b136-393366383035/36025351.jpg</t>
   </si>
   <si>
-    <t>https://static.tildacdn.com/stor6131-3935-4135-a633-343231653533/28860416.jpg</t>
-  </si>
-  <si>
     <t>https://static.tildacdn.com/stor3565-3038-4238-a231-383761363963/20895980.jpg</t>
   </si>
   <si>
@@ -3392,6 +3389,9 @@
   </si>
   <si>
     <t>No Mans Sky PS4/PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3362-6139-4537-a535-646463376538/-/format/webp/71185523.jpg</t>
   </si>
 </sst>
 </file>
@@ -3815,10 +3815,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>986</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3890,7 +3890,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -4042,7 +4042,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -4063,7 +4063,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>528</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>528</v>
@@ -4082,7 +4082,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -4194,7 +4194,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -4223,7 +4223,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>545</v>
@@ -4306,7 +4306,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -4314,7 +4314,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -4335,7 +4335,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>557</v>
@@ -4362,7 +4362,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -4618,7 +4618,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
@@ -4711,7 +4711,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>602</v>
@@ -4770,12 +4770,12 @@
         <v>113</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>609</v>
@@ -4874,7 +4874,7 @@
         <v>125</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
@@ -4951,7 +4951,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>630</v>
@@ -5098,7 +5098,7 @@
         <v>152</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
@@ -5298,7 +5298,7 @@
         <v>177</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
@@ -5314,7 +5314,7 @@
         <v>179</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
@@ -5351,7 +5351,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>677</v>
@@ -5370,7 +5370,7 @@
         <v>185</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
@@ -5383,7 +5383,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>680</v>
@@ -5482,7 +5482,7 @@
         <v>198</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
@@ -5506,7 +5506,7 @@
         <v>201</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
@@ -5530,7 +5530,7 @@
         <v>204</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
@@ -5594,7 +5594,7 @@
         <v>212</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
@@ -5810,7 +5810,7 @@
         <v>239</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
@@ -6015,7 +6015,7 @@
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>754</v>
@@ -6095,10 +6095,10 @@
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B286" s="2" t="s">
         <v>1123</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
@@ -6106,7 +6106,7 @@
         <v>274</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
@@ -6114,7 +6114,7 @@
         <v>275</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
@@ -6122,7 +6122,7 @@
         <v>276</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
@@ -6130,7 +6130,7 @@
         <v>277</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
@@ -6138,7 +6138,7 @@
         <v>278</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
@@ -6146,7 +6146,7 @@
         <v>279</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
@@ -6154,7 +6154,7 @@
         <v>280</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
@@ -6162,7 +6162,7 @@
         <v>281</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
@@ -6170,7 +6170,7 @@
         <v>282</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
@@ -6178,7 +6178,7 @@
         <v>283</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
@@ -6186,7 +6186,7 @@
         <v>284</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
@@ -6194,7 +6194,7 @@
         <v>285</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
@@ -6202,7 +6202,7 @@
         <v>286</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
@@ -6210,7 +6210,7 @@
         <v>287</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
@@ -6218,7 +6218,7 @@
         <v>288</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
@@ -6226,7 +6226,7 @@
         <v>289</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
@@ -6234,7 +6234,7 @@
         <v>290</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
@@ -6242,7 +6242,7 @@
         <v>291</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
@@ -6250,7 +6250,7 @@
         <v>292</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
@@ -6258,7 +6258,7 @@
         <v>293</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
@@ -6266,7 +6266,7 @@
         <v>294</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
@@ -6274,7 +6274,7 @@
         <v>295</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
@@ -6282,7 +6282,7 @@
         <v>296</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
@@ -6290,7 +6290,7 @@
         <v>297</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
@@ -6298,7 +6298,7 @@
         <v>298</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
@@ -6306,7 +6306,7 @@
         <v>299</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
@@ -6314,7 +6314,7 @@
         <v>300</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
@@ -6322,7 +6322,7 @@
         <v>301</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
@@ -6330,7 +6330,7 @@
         <v>302</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
@@ -6338,7 +6338,7 @@
         <v>303</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
@@ -6346,7 +6346,7 @@
         <v>304</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
@@ -6354,7 +6354,7 @@
         <v>305</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
@@ -6362,7 +6362,7 @@
         <v>306</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
@@ -6370,7 +6370,7 @@
         <v>307</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
@@ -6378,7 +6378,7 @@
         <v>308</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
@@ -6386,7 +6386,7 @@
         <v>309</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
@@ -6394,7 +6394,7 @@
         <v>310</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
@@ -6410,7 +6410,7 @@
         <v>311</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
@@ -6418,7 +6418,7 @@
         <v>312</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
@@ -6426,7 +6426,7 @@
         <v>313</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
@@ -6434,7 +6434,7 @@
         <v>314</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
@@ -6442,7 +6442,7 @@
         <v>315</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
@@ -6450,7 +6450,7 @@
         <v>316</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
@@ -6458,7 +6458,7 @@
         <v>317</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
@@ -6466,7 +6466,7 @@
         <v>318</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
@@ -6474,7 +6474,7 @@
         <v>319</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
@@ -6482,7 +6482,7 @@
         <v>320</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
@@ -6490,7 +6490,7 @@
         <v>321</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
@@ -6498,7 +6498,7 @@
         <v>322</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
@@ -6506,7 +6506,7 @@
         <v>323</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
@@ -6514,7 +6514,7 @@
         <v>324</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
@@ -6522,7 +6522,7 @@
         <v>325</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
@@ -6530,7 +6530,7 @@
         <v>326</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
@@ -6538,7 +6538,7 @@
         <v>327</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
@@ -6546,7 +6546,7 @@
         <v>328</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
@@ -6554,7 +6554,7 @@
         <v>329</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
@@ -6562,7 +6562,7 @@
         <v>330</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
@@ -6570,7 +6570,7 @@
         <v>331</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
@@ -6578,7 +6578,7 @@
         <v>332</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
@@ -6586,7 +6586,7 @@
         <v>333</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
@@ -6594,7 +6594,7 @@
         <v>334</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.2">
@@ -6602,7 +6602,7 @@
         <v>335</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.2">
@@ -6610,7 +6610,7 @@
         <v>336</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
@@ -6618,7 +6618,7 @@
         <v>337</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.2">
@@ -6626,7 +6626,7 @@
         <v>338</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.2">
@@ -6634,7 +6634,7 @@
         <v>339</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.2">
@@ -6642,7 +6642,7 @@
         <v>340</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.2">
@@ -6650,7 +6650,7 @@
         <v>341</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.2">
@@ -6658,7 +6658,7 @@
         <v>342</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.2">
@@ -6666,7 +6666,7 @@
         <v>343</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.2">
@@ -6674,7 +6674,7 @@
         <v>344</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
@@ -6682,7 +6682,7 @@
         <v>345</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.2">
@@ -6690,7 +6690,7 @@
         <v>346</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.2">
@@ -6698,7 +6698,7 @@
         <v>347</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.2">
@@ -6706,7 +6706,7 @@
         <v>348</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.2">
@@ -6714,7 +6714,7 @@
         <v>349</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.2">
@@ -6722,7 +6722,7 @@
         <v>350</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.2">
@@ -6730,7 +6730,7 @@
         <v>6</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.2">
@@ -6738,7 +6738,7 @@
         <v>351</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
@@ -6746,7 +6746,7 @@
         <v>352</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.2">
@@ -6754,7 +6754,7 @@
         <v>353</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
@@ -6762,7 +6762,7 @@
         <v>354</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
@@ -6770,7 +6770,7 @@
         <v>355</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
@@ -6778,7 +6778,7 @@
         <v>356</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
@@ -6786,7 +6786,7 @@
         <v>357</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
@@ -6794,7 +6794,7 @@
         <v>358</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
@@ -6802,15 +6802,15 @@
         <v>359</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
@@ -6818,7 +6818,7 @@
         <v>360</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
@@ -6826,7 +6826,7 @@
         <v>361</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
@@ -6834,7 +6834,7 @@
         <v>362</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
@@ -6842,7 +6842,7 @@
         <v>363</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
@@ -6850,7 +6850,7 @@
         <v>364</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
@@ -6858,7 +6858,7 @@
         <v>365</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
@@ -6866,7 +6866,7 @@
         <v>366</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
@@ -6874,7 +6874,7 @@
         <v>367</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
@@ -6882,7 +6882,7 @@
         <v>368</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
@@ -6890,7 +6890,7 @@
         <v>369</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
@@ -6898,7 +6898,7 @@
         <v>370</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
@@ -6906,7 +6906,7 @@
         <v>371</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
@@ -6914,7 +6914,7 @@
         <v>372</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
@@ -6922,7 +6922,7 @@
         <v>373</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
@@ -6930,7 +6930,7 @@
         <v>374</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
@@ -6938,7 +6938,7 @@
         <v>375</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
@@ -6946,7 +6946,7 @@
         <v>376</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
@@ -6954,7 +6954,7 @@
         <v>377</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
@@ -6962,7 +6962,7 @@
         <v>378</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
@@ -6970,7 +6970,7 @@
         <v>379</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
@@ -6978,7 +6978,7 @@
         <v>380</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
@@ -6986,7 +6986,7 @@
         <v>381</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
@@ -6994,7 +6994,7 @@
         <v>382</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
@@ -7002,7 +7002,7 @@
         <v>383</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
@@ -7010,7 +7010,7 @@
         <v>384</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
@@ -7018,7 +7018,7 @@
         <v>385</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
@@ -7026,7 +7026,7 @@
         <v>386</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
@@ -7034,7 +7034,7 @@
         <v>387</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
@@ -7042,7 +7042,7 @@
         <v>388</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
@@ -7050,7 +7050,7 @@
         <v>389</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
@@ -7058,7 +7058,7 @@
         <v>390</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
@@ -7066,7 +7066,7 @@
         <v>391</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
@@ -7074,7 +7074,7 @@
         <v>392</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
@@ -7082,7 +7082,7 @@
         <v>393</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
@@ -7090,7 +7090,7 @@
         <v>394</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
@@ -7098,7 +7098,7 @@
         <v>395</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
@@ -7106,7 +7106,7 @@
         <v>396</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
@@ -7114,7 +7114,7 @@
         <v>397</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
@@ -7122,7 +7122,7 @@
         <v>398</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
@@ -7130,7 +7130,7 @@
         <v>399</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
@@ -7138,15 +7138,15 @@
         <v>400</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B417" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
@@ -7154,7 +7154,7 @@
         <v>401</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.2">
@@ -7162,7 +7162,7 @@
         <v>402</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
@@ -7170,7 +7170,7 @@
         <v>403</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.2">
@@ -7178,7 +7178,7 @@
         <v>404</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.2">
@@ -7186,7 +7186,7 @@
         <v>405</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.2">
@@ -7194,7 +7194,7 @@
         <v>406</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.2">
@@ -7202,7 +7202,7 @@
         <v>407</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
@@ -7210,7 +7210,7 @@
         <v>408</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.2">
@@ -7218,7 +7218,7 @@
         <v>409</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.2">
@@ -7226,7 +7226,7 @@
         <v>410</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
@@ -7234,7 +7234,7 @@
         <v>411</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.2">
@@ -7242,7 +7242,7 @@
         <v>412</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.2">
@@ -7250,7 +7250,7 @@
         <v>413</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.2">
@@ -7258,7 +7258,7 @@
         <v>414</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
@@ -7266,7 +7266,7 @@
         <v>415</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.2">
@@ -7274,7 +7274,7 @@
         <v>416</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.2">
@@ -7282,7 +7282,7 @@
         <v>417</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.2">
@@ -7290,7 +7290,7 @@
         <v>418</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.2">
@@ -7298,7 +7298,7 @@
         <v>419</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.2">
@@ -7306,7 +7306,7 @@
         <v>420</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.2">
@@ -7314,7 +7314,7 @@
         <v>421</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
@@ -7322,7 +7322,7 @@
         <v>422</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
@@ -7330,7 +7330,7 @@
         <v>423</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
@@ -7338,7 +7338,7 @@
         <v>424</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
@@ -7346,7 +7346,7 @@
         <v>425</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
@@ -7354,7 +7354,7 @@
         <v>426</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
@@ -7362,7 +7362,7 @@
         <v>427</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
@@ -7370,7 +7370,7 @@
         <v>428</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
@@ -7378,7 +7378,7 @@
         <v>429</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
@@ -7386,7 +7386,7 @@
         <v>430</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
@@ -7394,7 +7394,7 @@
         <v>431</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
@@ -7402,7 +7402,7 @@
         <v>432</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
@@ -7410,7 +7410,7 @@
         <v>433</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
@@ -7418,7 +7418,7 @@
         <v>434</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
@@ -7426,7 +7426,7 @@
         <v>435</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
@@ -7434,7 +7434,7 @@
         <v>436</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
@@ -7442,7 +7442,7 @@
         <v>437</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
@@ -7450,7 +7450,7 @@
         <v>438</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
@@ -7458,7 +7458,7 @@
         <v>439</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
@@ -7466,7 +7466,7 @@
         <v>440</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
@@ -7474,7 +7474,7 @@
         <v>441</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
@@ -7482,7 +7482,7 @@
         <v>442</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
@@ -7490,7 +7490,7 @@
         <v>443</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
@@ -7498,7 +7498,7 @@
         <v>444</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
@@ -7506,7 +7506,7 @@
         <v>445</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
@@ -7514,7 +7514,7 @@
         <v>446</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
@@ -7522,7 +7522,7 @@
         <v>447</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
@@ -7530,7 +7530,7 @@
         <v>448</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
@@ -7538,7 +7538,7 @@
         <v>449</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
@@ -7546,7 +7546,7 @@
         <v>450</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
@@ -7554,7 +7554,7 @@
         <v>451</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
@@ -7562,7 +7562,7 @@
         <v>452</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
@@ -7570,7 +7570,7 @@
         <v>453</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
@@ -7578,7 +7578,7 @@
         <v>454</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
@@ -7586,7 +7586,7 @@
         <v>455</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
@@ -7594,7 +7594,7 @@
         <v>456</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
@@ -7602,7 +7602,7 @@
         <v>457</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
@@ -7610,7 +7610,7 @@
         <v>458</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
@@ -7618,7 +7618,7 @@
         <v>459</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">
@@ -7626,7 +7626,7 @@
         <v>460</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
@@ -7634,7 +7634,7 @@
         <v>461</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
@@ -7642,7 +7642,7 @@
         <v>462</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
@@ -7650,7 +7650,7 @@
         <v>463</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.2">
@@ -7658,7 +7658,7 @@
         <v>464</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
@@ -7666,7 +7666,7 @@
         <v>465</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.2">
@@ -7674,15 +7674,15 @@
         <v>466</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.2">
@@ -7690,7 +7690,7 @@
         <v>467</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
@@ -7698,7 +7698,7 @@
         <v>468</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.2">
@@ -7706,7 +7706,7 @@
         <v>469</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.2">
@@ -7714,7 +7714,7 @@
         <v>470</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.2">
@@ -7722,7 +7722,7 @@
         <v>471</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.2">
@@ -7730,7 +7730,7 @@
         <v>472</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.2">
@@ -7738,7 +7738,7 @@
         <v>473</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.2">
@@ -7746,7 +7746,7 @@
         <v>474</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.2">
@@ -7754,7 +7754,7 @@
         <v>475</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.2">
@@ -7762,7 +7762,7 @@
         <v>476</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.2">
@@ -7770,7 +7770,7 @@
         <v>477</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.2">
@@ -7778,7 +7778,7 @@
         <v>478</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
@@ -7786,7 +7786,7 @@
         <v>479</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
@@ -7794,7 +7794,7 @@
         <v>480</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
@@ -7802,7 +7802,7 @@
         <v>481</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
@@ -7810,7 +7810,7 @@
         <v>482</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
@@ -7818,7 +7818,7 @@
         <v>483</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.2">
@@ -7826,7 +7826,7 @@
         <v>484</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.2">
@@ -7834,7 +7834,7 @@
         <v>485</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
@@ -7842,7 +7842,7 @@
         <v>486</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
@@ -7850,7 +7850,7 @@
         <v>487</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
@@ -7858,7 +7858,7 @@
         <v>488</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
@@ -7866,7 +7866,7 @@
         <v>489</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
@@ -7874,7 +7874,7 @@
         <v>490</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
@@ -7882,7 +7882,7 @@
         <v>491</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
@@ -7890,7 +7890,7 @@
         <v>492</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
@@ -7898,15 +7898,15 @@
         <v>493</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.2">
@@ -7914,7 +7914,7 @@
         <v>494</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.2">
@@ -7922,15 +7922,15 @@
         <v>495</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.2">
@@ -7938,7 +7938,7 @@
         <v>496</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.2">
@@ -7946,7 +7946,7 @@
         <v>497</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.2">
@@ -7954,7 +7954,7 @@
         <v>498</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.2">
@@ -7962,383 +7962,383 @@
         <v>499</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B522" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B523" t="s">
         <v>1010</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B524" t="s">
         <v>1012</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B525" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B526" t="s">
         <v>1026</v>
-      </c>
-      <c r="B526" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B527" t="s">
         <v>1028</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B528" t="s">
         <v>1031</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B529" t="s">
         <v>1037</v>
-      </c>
-      <c r="B529" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B530" t="s">
         <v>1039</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B531" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B532" t="s">
         <v>1047</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B533" t="s">
         <v>1049</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B534" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B535" t="s">
         <v>1055</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B536" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B537" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B538" t="s">
         <v>1061</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B539" t="s">
         <v>1063</v>
-      </c>
-      <c r="B539" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B540" t="s">
         <v>1065</v>
-      </c>
-      <c r="B540" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B541" t="s">
         <v>1067</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B542" t="s">
         <v>1069</v>
-      </c>
-      <c r="B542" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B543" t="s">
         <v>1071</v>
-      </c>
-      <c r="B543" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B544" t="s">
         <v>1073</v>
-      </c>
-      <c r="B544" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B545" t="s">
         <v>1075</v>
-      </c>
-      <c r="B545" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B546" t="s">
         <v>1077</v>
-      </c>
-      <c r="B546" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B547" t="s">
         <v>1079</v>
-      </c>
-      <c r="B547" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B548" t="s">
         <v>1081</v>
-      </c>
-      <c r="B548" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B549" t="s">
         <v>1083</v>
-      </c>
-      <c r="B549" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B550" t="s">
         <v>1085</v>
-      </c>
-      <c r="B550" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B551" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B552" t="s">
         <v>1089</v>
-      </c>
-      <c r="B552" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B553" t="s">
         <v>1092</v>
-      </c>
-      <c r="B553" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B554" t="s">
         <v>1097</v>
-      </c>
-      <c r="B554" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B555" t="s">
         <v>1095</v>
-      </c>
-      <c r="B555" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B556" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B557" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B558" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B559" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B560" t="s">
         <v>1108</v>
-      </c>
-      <c r="B560" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B561" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B562" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B563" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B564" t="s">
         <v>1117</v>
-      </c>
-      <c r="B564" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B565" t="s">
         <v>1119</v>
-      </c>
-      <c r="B565" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B566" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
@@ -8620,7 +8620,7 @@
     <hyperlink ref="B283" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
     <hyperlink ref="B284" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
     <hyperlink ref="B285" r:id="rId277" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="B286" r:id="rId278" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="B286" r:id="rId278" display="https://static.tildacdn.com/stor6131-3935-4135-a633-343231653533/28860416.jpg" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
     <hyperlink ref="B287" r:id="rId279" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
     <hyperlink ref="B288" r:id="rId280" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
     <hyperlink ref="B289" r:id="rId281" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489CDAD2-FB32-784D-A02F-8C812E747A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3B8317-B505-7647-9CCA-0710E53BEFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="1126">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3392,6 +3392,12 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor3362-6139-4537-a535-646463376538/-/format/webp/71185523.jpg</t>
+  </si>
+  <si>
+    <t>Atomic Heart: Узник Лимбо PS4/PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3034-3063-4432-b834-356230623561/-/format/webp/6ee6f05ea9a72566789bc4c3ae5685ce.jpg</t>
   </si>
 </sst>
 </file>
@@ -3806,7 +3812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B566"/>
+  <dimension ref="A1:B567"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8339,6 +8345,14 @@
       </c>
       <c r="B566" t="s">
         <v>1120</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A567" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1125</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3B8317-B505-7647-9CCA-0710E53BEFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BCAE9E-7975-1A48-8826-46B7B45CC572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1777,9 +1777,6 @@
     <t>https://static.tildacdn.com/stor3465-6566-4132-b537-313536333464/87035029.jpg</t>
   </si>
   <si>
-    <t>https://static.tildacdn.com/stor6230-3138-4833-b439-343538643038/19031351.jpg</t>
-  </si>
-  <si>
     <t>https://static.tildacdn.com/stor3930-6436-4930-b132-383737613639/15052717.jpg</t>
   </si>
   <si>
@@ -3398,6 +3395,9 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor3034-3063-4432-b834-356230623561/-/format/webp/6ee6f05ea9a72566789bc4c3ae5685ce.jpg</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3638-6231-4432-b831-333763316336/-/format/webp/80741907.jpg</t>
   </si>
 </sst>
 </file>
@@ -3821,10 +3821,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>985</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3896,7 +3896,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -4048,7 +4048,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -4069,7 +4069,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>528</v>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>528</v>
@@ -4088,7 +4088,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -4200,7 +4200,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -4229,7 +4229,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>545</v>
@@ -4312,7 +4312,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -4320,7 +4320,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -4341,7 +4341,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>557</v>
@@ -4368,7 +4368,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -4576,7 +4576,7 @@
         <v>89</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>585</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
@@ -4584,7 +4584,7 @@
         <v>90</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
@@ -4592,7 +4592,7 @@
         <v>91</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
@@ -4600,7 +4600,7 @@
         <v>92</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
@@ -4608,7 +4608,7 @@
         <v>93</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
@@ -4616,7 +4616,7 @@
         <v>94</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
@@ -4624,7 +4624,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
@@ -4632,7 +4632,7 @@
         <v>96</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
@@ -4640,7 +4640,7 @@
         <v>97</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
@@ -4648,7 +4648,7 @@
         <v>98</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
@@ -4656,7 +4656,7 @@
         <v>99</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
@@ -4664,7 +4664,7 @@
         <v>100</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
@@ -4672,7 +4672,7 @@
         <v>101</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
@@ -4680,7 +4680,7 @@
         <v>102</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
@@ -4688,7 +4688,7 @@
         <v>103</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
@@ -4696,7 +4696,7 @@
         <v>104</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
@@ -4704,7 +4704,7 @@
         <v>105</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
@@ -4712,15 +4712,15 @@
         <v>106</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
@@ -4728,7 +4728,7 @@
         <v>107</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
@@ -4736,7 +4736,7 @@
         <v>108</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
@@ -4744,7 +4744,7 @@
         <v>109</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
@@ -4752,7 +4752,7 @@
         <v>110</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
@@ -4760,7 +4760,7 @@
         <v>111</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
@@ -4768,7 +4768,7 @@
         <v>112</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
@@ -4776,15 +4776,15 @@
         <v>113</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
@@ -4792,7 +4792,7 @@
         <v>114</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
@@ -4800,7 +4800,7 @@
         <v>115</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
@@ -4808,7 +4808,7 @@
         <v>116</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
@@ -4816,7 +4816,7 @@
         <v>117</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
@@ -4824,7 +4824,7 @@
         <v>118</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
@@ -4832,7 +4832,7 @@
         <v>119</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
@@ -4840,7 +4840,7 @@
         <v>120</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
@@ -4848,7 +4848,7 @@
         <v>121</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
@@ -4856,7 +4856,7 @@
         <v>122</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
@@ -4864,7 +4864,7 @@
         <v>123</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
@@ -4872,7 +4872,7 @@
         <v>124</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
@@ -4880,7 +4880,7 @@
         <v>125</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
@@ -4888,7 +4888,7 @@
         <v>126</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
@@ -4896,7 +4896,7 @@
         <v>127</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
@@ -4904,7 +4904,7 @@
         <v>128</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
@@ -4912,7 +4912,7 @@
         <v>129</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
@@ -4920,7 +4920,7 @@
         <v>130</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
@@ -4928,7 +4928,7 @@
         <v>131</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
@@ -4936,7 +4936,7 @@
         <v>132</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
@@ -4944,7 +4944,7 @@
         <v>133</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
@@ -4952,15 +4952,15 @@
         <v>134</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
@@ -4968,7 +4968,7 @@
         <v>135</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
@@ -4976,7 +4976,7 @@
         <v>136</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
@@ -4984,7 +4984,7 @@
         <v>137</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
@@ -4992,7 +4992,7 @@
         <v>138</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
@@ -5000,7 +5000,7 @@
         <v>139</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
@@ -5008,7 +5008,7 @@
         <v>140</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
@@ -5016,7 +5016,7 @@
         <v>141</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
@@ -5024,7 +5024,7 @@
         <v>142</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
@@ -5032,7 +5032,7 @@
         <v>143</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
@@ -5040,7 +5040,7 @@
         <v>144</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
@@ -5048,7 +5048,7 @@
         <v>145</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
@@ -5056,7 +5056,7 @@
         <v>146</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
@@ -5064,7 +5064,7 @@
         <v>147</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
@@ -5072,7 +5072,7 @@
         <v>148</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
@@ -5080,7 +5080,7 @@
         <v>149</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
@@ -5088,7 +5088,7 @@
         <v>150</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
@@ -5096,7 +5096,7 @@
         <v>151</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
@@ -5104,7 +5104,7 @@
         <v>152</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
@@ -5112,7 +5112,7 @@
         <v>153</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
@@ -5120,7 +5120,7 @@
         <v>154</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
@@ -5128,7 +5128,7 @@
         <v>155</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
@@ -5136,7 +5136,7 @@
         <v>156</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
@@ -5144,7 +5144,7 @@
         <v>157</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
@@ -5152,7 +5152,7 @@
         <v>158</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
@@ -5160,7 +5160,7 @@
         <v>159</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
@@ -5168,7 +5168,7 @@
         <v>160</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
@@ -5176,7 +5176,7 @@
         <v>161</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
@@ -5184,7 +5184,7 @@
         <v>162</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
@@ -5192,7 +5192,7 @@
         <v>163</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
@@ -5200,7 +5200,7 @@
         <v>164</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
@@ -5208,7 +5208,7 @@
         <v>165</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
@@ -5216,7 +5216,7 @@
         <v>166</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
@@ -5224,7 +5224,7 @@
         <v>167</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
@@ -5232,7 +5232,7 @@
         <v>168</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
@@ -5240,7 +5240,7 @@
         <v>169</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
@@ -5248,7 +5248,7 @@
         <v>170</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
@@ -5256,7 +5256,7 @@
         <v>171</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
@@ -5264,7 +5264,7 @@
         <v>172</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
@@ -5272,7 +5272,7 @@
         <v>173</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
@@ -5280,7 +5280,7 @@
         <v>174</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
@@ -5288,7 +5288,7 @@
         <v>175</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
@@ -5296,7 +5296,7 @@
         <v>176</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
@@ -5304,7 +5304,7 @@
         <v>177</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
@@ -5312,7 +5312,7 @@
         <v>178</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
@@ -5320,7 +5320,7 @@
         <v>179</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
@@ -5328,7 +5328,7 @@
         <v>180</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
@@ -5336,7 +5336,7 @@
         <v>181</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
@@ -5344,7 +5344,7 @@
         <v>182</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
@@ -5352,15 +5352,15 @@
         <v>183</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
@@ -5368,7 +5368,7 @@
         <v>184</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
@@ -5376,7 +5376,7 @@
         <v>185</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
@@ -5384,15 +5384,15 @@
         <v>186</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
@@ -5400,7 +5400,7 @@
         <v>187</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
@@ -5408,7 +5408,7 @@
         <v>188</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
@@ -5416,7 +5416,7 @@
         <v>189</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
@@ -5424,7 +5424,7 @@
         <v>190</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
@@ -5432,7 +5432,7 @@
         <v>191</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
@@ -5440,7 +5440,7 @@
         <v>192</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
@@ -5448,7 +5448,7 @@
         <v>193</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
@@ -5456,7 +5456,7 @@
         <v>194</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
@@ -5464,7 +5464,7 @@
         <v>195</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
@@ -5472,7 +5472,7 @@
         <v>196</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
@@ -5480,7 +5480,7 @@
         <v>197</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
@@ -5488,7 +5488,7 @@
         <v>198</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
@@ -5496,7 +5496,7 @@
         <v>199</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
@@ -5504,7 +5504,7 @@
         <v>200</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
@@ -5512,7 +5512,7 @@
         <v>201</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
@@ -5520,7 +5520,7 @@
         <v>202</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
@@ -5528,7 +5528,7 @@
         <v>203</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
@@ -5536,7 +5536,7 @@
         <v>204</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
@@ -5544,7 +5544,7 @@
         <v>205</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
@@ -5552,7 +5552,7 @@
         <v>206</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
@@ -5560,7 +5560,7 @@
         <v>207</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
@@ -5568,7 +5568,7 @@
         <v>208</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
@@ -5576,7 +5576,7 @@
         <v>209</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
@@ -5584,7 +5584,7 @@
         <v>210</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
@@ -5592,7 +5592,7 @@
         <v>211</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
@@ -5600,7 +5600,7 @@
         <v>212</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
@@ -5608,7 +5608,7 @@
         <v>213</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
@@ -5616,7 +5616,7 @@
         <v>214</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
@@ -5624,7 +5624,7 @@
         <v>215</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
@@ -5632,7 +5632,7 @@
         <v>216</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
@@ -5640,7 +5640,7 @@
         <v>217</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
@@ -5648,7 +5648,7 @@
         <v>218</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
@@ -5656,7 +5656,7 @@
         <v>219</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
@@ -5664,7 +5664,7 @@
         <v>220</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
@@ -5672,7 +5672,7 @@
         <v>221</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
@@ -5680,7 +5680,7 @@
         <v>222</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
@@ -5688,7 +5688,7 @@
         <v>223</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
@@ -5696,7 +5696,7 @@
         <v>224</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
@@ -5704,7 +5704,7 @@
         <v>225</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
@@ -5712,7 +5712,7 @@
         <v>226</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
@@ -5720,7 +5720,7 @@
         <v>227</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
@@ -5728,7 +5728,7 @@
         <v>228</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
@@ -5736,7 +5736,7 @@
         <v>229</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
@@ -5744,7 +5744,7 @@
         <v>230</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
@@ -5752,7 +5752,7 @@
         <v>231</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
@@ -5760,7 +5760,7 @@
         <v>232</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
@@ -5768,7 +5768,7 @@
         <v>233</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
@@ -5776,7 +5776,7 @@
         <v>234</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
@@ -5784,7 +5784,7 @@
         <v>235</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
@@ -5792,7 +5792,7 @@
         <v>236</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
@@ -5800,7 +5800,7 @@
         <v>237</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
@@ -5808,7 +5808,7 @@
         <v>238</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
@@ -5816,7 +5816,7 @@
         <v>239</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
@@ -5824,7 +5824,7 @@
         <v>240</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
@@ -5832,7 +5832,7 @@
         <v>241</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
@@ -5840,7 +5840,7 @@
         <v>242</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
@@ -5848,7 +5848,7 @@
         <v>243</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
@@ -5856,7 +5856,7 @@
         <v>244</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
@@ -5864,7 +5864,7 @@
         <v>245</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
@@ -5872,7 +5872,7 @@
         <v>246</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
@@ -5880,7 +5880,7 @@
         <v>247</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
@@ -5888,7 +5888,7 @@
         <v>248</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
@@ -5896,7 +5896,7 @@
         <v>249</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
@@ -5904,7 +5904,7 @@
         <v>250</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
@@ -5912,7 +5912,7 @@
         <v>251</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
@@ -5920,7 +5920,7 @@
         <v>252</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
@@ -5928,7 +5928,7 @@
         <v>253</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
@@ -5936,7 +5936,7 @@
         <v>254</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
@@ -5944,7 +5944,7 @@
         <v>255</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
@@ -5952,7 +5952,7 @@
         <v>256</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
@@ -5960,7 +5960,7 @@
         <v>257</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
@@ -5968,7 +5968,7 @@
         <v>258</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
@@ -5976,7 +5976,7 @@
         <v>259</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
@@ -5984,7 +5984,7 @@
         <v>260</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
@@ -5992,7 +5992,7 @@
         <v>261</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
@@ -6000,7 +6000,7 @@
         <v>262</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
@@ -6008,7 +6008,7 @@
         <v>263</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
@@ -6016,15 +6016,15 @@
         <v>264</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
@@ -6032,7 +6032,7 @@
         <v>265</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
@@ -6040,7 +6040,7 @@
         <v>266</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
@@ -6048,7 +6048,7 @@
         <v>267</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
@@ -6056,7 +6056,7 @@
         <v>268</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
@@ -6064,7 +6064,7 @@
         <v>269</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
@@ -6072,7 +6072,7 @@
         <v>270</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
@@ -6080,7 +6080,7 @@
         <v>271</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
@@ -6088,7 +6088,7 @@
         <v>272</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
@@ -6096,15 +6096,15 @@
         <v>273</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B286" s="2" t="s">
         <v>1122</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
@@ -6112,7 +6112,7 @@
         <v>274</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
@@ -6120,7 +6120,7 @@
         <v>275</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
@@ -6128,7 +6128,7 @@
         <v>276</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
@@ -6136,7 +6136,7 @@
         <v>277</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
@@ -6144,7 +6144,7 @@
         <v>278</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
@@ -6152,7 +6152,7 @@
         <v>279</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
@@ -6160,7 +6160,7 @@
         <v>280</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
@@ -6168,7 +6168,7 @@
         <v>281</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
@@ -6176,7 +6176,7 @@
         <v>282</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
@@ -6184,7 +6184,7 @@
         <v>283</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
@@ -6192,7 +6192,7 @@
         <v>284</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
@@ -6200,7 +6200,7 @@
         <v>285</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
@@ -6208,7 +6208,7 @@
         <v>286</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
@@ -6216,7 +6216,7 @@
         <v>287</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
@@ -6224,7 +6224,7 @@
         <v>288</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
@@ -6232,7 +6232,7 @@
         <v>289</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
@@ -6240,7 +6240,7 @@
         <v>290</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
@@ -6248,7 +6248,7 @@
         <v>291</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
@@ -6256,7 +6256,7 @@
         <v>292</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
@@ -6264,7 +6264,7 @@
         <v>293</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
@@ -6272,7 +6272,7 @@
         <v>294</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
@@ -6280,7 +6280,7 @@
         <v>295</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
@@ -6288,7 +6288,7 @@
         <v>296</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
@@ -6296,7 +6296,7 @@
         <v>297</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
@@ -6304,7 +6304,7 @@
         <v>298</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
@@ -6312,7 +6312,7 @@
         <v>299</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
@@ -6320,7 +6320,7 @@
         <v>300</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
@@ -6328,7 +6328,7 @@
         <v>301</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
@@ -6336,7 +6336,7 @@
         <v>302</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
@@ -6344,7 +6344,7 @@
         <v>303</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
@@ -6352,7 +6352,7 @@
         <v>304</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
@@ -6360,7 +6360,7 @@
         <v>305</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
@@ -6368,7 +6368,7 @@
         <v>306</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
@@ -6376,7 +6376,7 @@
         <v>307</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
@@ -6384,7 +6384,7 @@
         <v>308</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
@@ -6392,7 +6392,7 @@
         <v>309</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
@@ -6400,7 +6400,7 @@
         <v>310</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
@@ -6416,7 +6416,7 @@
         <v>311</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
@@ -6424,7 +6424,7 @@
         <v>312</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
@@ -6432,7 +6432,7 @@
         <v>313</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
@@ -6440,7 +6440,7 @@
         <v>314</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
@@ -6448,7 +6448,7 @@
         <v>315</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
@@ -6456,7 +6456,7 @@
         <v>316</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
@@ -6464,7 +6464,7 @@
         <v>317</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
@@ -6472,7 +6472,7 @@
         <v>318</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
@@ -6480,7 +6480,7 @@
         <v>319</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
@@ -6488,7 +6488,7 @@
         <v>320</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
@@ -6496,7 +6496,7 @@
         <v>321</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
@@ -6504,7 +6504,7 @@
         <v>322</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
@@ -6512,7 +6512,7 @@
         <v>323</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
@@ -6520,7 +6520,7 @@
         <v>324</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
@@ -6528,7 +6528,7 @@
         <v>325</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
@@ -6536,7 +6536,7 @@
         <v>326</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
@@ -6544,7 +6544,7 @@
         <v>327</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
@@ -6552,7 +6552,7 @@
         <v>328</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
@@ -6560,7 +6560,7 @@
         <v>329</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
@@ -6568,7 +6568,7 @@
         <v>330</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
@@ -6576,7 +6576,7 @@
         <v>331</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
@@ -6584,7 +6584,7 @@
         <v>332</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
@@ -6592,7 +6592,7 @@
         <v>333</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
@@ -6600,7 +6600,7 @@
         <v>334</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.2">
@@ -6608,7 +6608,7 @@
         <v>335</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.2">
@@ -6616,7 +6616,7 @@
         <v>336</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
@@ -6624,7 +6624,7 @@
         <v>337</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.2">
@@ -6632,7 +6632,7 @@
         <v>338</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.2">
@@ -6640,7 +6640,7 @@
         <v>339</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.2">
@@ -6648,7 +6648,7 @@
         <v>340</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.2">
@@ -6656,7 +6656,7 @@
         <v>341</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.2">
@@ -6664,7 +6664,7 @@
         <v>342</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.2">
@@ -6672,7 +6672,7 @@
         <v>343</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.2">
@@ -6680,7 +6680,7 @@
         <v>344</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
@@ -6688,7 +6688,7 @@
         <v>345</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.2">
@@ -6696,7 +6696,7 @@
         <v>346</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.2">
@@ -6704,7 +6704,7 @@
         <v>347</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.2">
@@ -6712,7 +6712,7 @@
         <v>348</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.2">
@@ -6720,7 +6720,7 @@
         <v>349</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.2">
@@ -6728,7 +6728,7 @@
         <v>350</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.2">
@@ -6736,7 +6736,7 @@
         <v>6</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.2">
@@ -6744,7 +6744,7 @@
         <v>351</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
@@ -6752,7 +6752,7 @@
         <v>352</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.2">
@@ -6760,7 +6760,7 @@
         <v>353</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
@@ -6768,7 +6768,7 @@
         <v>354</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
@@ -6776,7 +6776,7 @@
         <v>355</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
@@ -6784,7 +6784,7 @@
         <v>356</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
@@ -6792,7 +6792,7 @@
         <v>357</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
@@ -6800,7 +6800,7 @@
         <v>358</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
@@ -6808,15 +6808,15 @@
         <v>359</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
@@ -6824,7 +6824,7 @@
         <v>360</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
@@ -6832,7 +6832,7 @@
         <v>361</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
@@ -6840,7 +6840,7 @@
         <v>362</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
@@ -6848,7 +6848,7 @@
         <v>363</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
@@ -6856,7 +6856,7 @@
         <v>364</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
@@ -6864,7 +6864,7 @@
         <v>365</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
@@ -6872,7 +6872,7 @@
         <v>366</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
@@ -6880,7 +6880,7 @@
         <v>367</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
@@ -6888,7 +6888,7 @@
         <v>368</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
@@ -6896,7 +6896,7 @@
         <v>369</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
@@ -6904,7 +6904,7 @@
         <v>370</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
@@ -6912,7 +6912,7 @@
         <v>371</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
@@ -6920,7 +6920,7 @@
         <v>372</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
@@ -6928,7 +6928,7 @@
         <v>373</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
@@ -6936,7 +6936,7 @@
         <v>374</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
@@ -6944,7 +6944,7 @@
         <v>375</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
@@ -6952,7 +6952,7 @@
         <v>376</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
@@ -6960,7 +6960,7 @@
         <v>377</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
@@ -6968,7 +6968,7 @@
         <v>378</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
@@ -6976,7 +6976,7 @@
         <v>379</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
@@ -6984,7 +6984,7 @@
         <v>380</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
@@ -6992,7 +6992,7 @@
         <v>381</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
@@ -7000,7 +7000,7 @@
         <v>382</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
@@ -7008,7 +7008,7 @@
         <v>383</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
@@ -7016,7 +7016,7 @@
         <v>384</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
@@ -7024,7 +7024,7 @@
         <v>385</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
@@ -7032,7 +7032,7 @@
         <v>386</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
@@ -7040,7 +7040,7 @@
         <v>387</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
@@ -7048,7 +7048,7 @@
         <v>388</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
@@ -7056,7 +7056,7 @@
         <v>389</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
@@ -7064,7 +7064,7 @@
         <v>390</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
@@ -7072,7 +7072,7 @@
         <v>391</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
@@ -7080,7 +7080,7 @@
         <v>392</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
@@ -7088,7 +7088,7 @@
         <v>393</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
@@ -7096,7 +7096,7 @@
         <v>394</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
@@ -7104,7 +7104,7 @@
         <v>395</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
@@ -7112,7 +7112,7 @@
         <v>396</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
@@ -7120,7 +7120,7 @@
         <v>397</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
@@ -7128,7 +7128,7 @@
         <v>398</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
@@ -7136,7 +7136,7 @@
         <v>399</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
@@ -7144,15 +7144,15 @@
         <v>400</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B417" s="2" t="s">
         <v>1017</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
@@ -7160,7 +7160,7 @@
         <v>401</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.2">
@@ -7168,7 +7168,7 @@
         <v>402</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
@@ -7176,7 +7176,7 @@
         <v>403</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.2">
@@ -7184,7 +7184,7 @@
         <v>404</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.2">
@@ -7192,7 +7192,7 @@
         <v>405</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.2">
@@ -7200,7 +7200,7 @@
         <v>406</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.2">
@@ -7208,7 +7208,7 @@
         <v>407</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
@@ -7216,7 +7216,7 @@
         <v>408</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.2">
@@ -7224,7 +7224,7 @@
         <v>409</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.2">
@@ -7232,7 +7232,7 @@
         <v>410</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
@@ -7240,7 +7240,7 @@
         <v>411</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.2">
@@ -7248,7 +7248,7 @@
         <v>412</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.2">
@@ -7256,7 +7256,7 @@
         <v>413</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.2">
@@ -7264,7 +7264,7 @@
         <v>414</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
@@ -7272,7 +7272,7 @@
         <v>415</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.2">
@@ -7280,7 +7280,7 @@
         <v>416</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.2">
@@ -7288,7 +7288,7 @@
         <v>417</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.2">
@@ -7296,7 +7296,7 @@
         <v>418</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.2">
@@ -7304,7 +7304,7 @@
         <v>419</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.2">
@@ -7312,7 +7312,7 @@
         <v>420</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.2">
@@ -7320,7 +7320,7 @@
         <v>421</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
@@ -7328,7 +7328,7 @@
         <v>422</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
@@ -7336,7 +7336,7 @@
         <v>423</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
@@ -7344,7 +7344,7 @@
         <v>424</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
@@ -7352,7 +7352,7 @@
         <v>425</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
@@ -7360,7 +7360,7 @@
         <v>426</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
@@ -7368,7 +7368,7 @@
         <v>427</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
@@ -7376,7 +7376,7 @@
         <v>428</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
@@ -7384,7 +7384,7 @@
         <v>429</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
@@ -7392,7 +7392,7 @@
         <v>430</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
@@ -7400,7 +7400,7 @@
         <v>431</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
@@ -7408,7 +7408,7 @@
         <v>432</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
@@ -7416,7 +7416,7 @@
         <v>433</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
@@ -7424,7 +7424,7 @@
         <v>434</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
@@ -7432,7 +7432,7 @@
         <v>435</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
@@ -7440,7 +7440,7 @@
         <v>436</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
@@ -7448,7 +7448,7 @@
         <v>437</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
@@ -7456,7 +7456,7 @@
         <v>438</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
@@ -7464,7 +7464,7 @@
         <v>439</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
@@ -7472,7 +7472,7 @@
         <v>440</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
@@ -7480,7 +7480,7 @@
         <v>441</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
@@ -7488,7 +7488,7 @@
         <v>442</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
@@ -7496,7 +7496,7 @@
         <v>443</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
@@ -7504,7 +7504,7 @@
         <v>444</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
@@ -7512,7 +7512,7 @@
         <v>445</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
@@ -7520,7 +7520,7 @@
         <v>446</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
@@ -7528,7 +7528,7 @@
         <v>447</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
@@ -7536,7 +7536,7 @@
         <v>448</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
@@ -7544,7 +7544,7 @@
         <v>449</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
@@ -7552,7 +7552,7 @@
         <v>450</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
@@ -7560,7 +7560,7 @@
         <v>451</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
@@ -7568,7 +7568,7 @@
         <v>452</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
@@ -7576,7 +7576,7 @@
         <v>453</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
@@ -7584,7 +7584,7 @@
         <v>454</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
@@ -7592,7 +7592,7 @@
         <v>455</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
@@ -7600,7 +7600,7 @@
         <v>456</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
@@ -7608,7 +7608,7 @@
         <v>457</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
@@ -7616,7 +7616,7 @@
         <v>458</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
@@ -7624,7 +7624,7 @@
         <v>459</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">
@@ -7632,7 +7632,7 @@
         <v>460</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
@@ -7640,7 +7640,7 @@
         <v>461</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
@@ -7648,7 +7648,7 @@
         <v>462</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
@@ -7656,7 +7656,7 @@
         <v>463</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.2">
@@ -7664,7 +7664,7 @@
         <v>464</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
@@ -7672,7 +7672,7 @@
         <v>465</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.2">
@@ -7680,15 +7680,15 @@
         <v>466</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.2">
@@ -7696,7 +7696,7 @@
         <v>467</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
@@ -7704,7 +7704,7 @@
         <v>468</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.2">
@@ -7712,7 +7712,7 @@
         <v>469</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.2">
@@ -7720,7 +7720,7 @@
         <v>470</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.2">
@@ -7728,7 +7728,7 @@
         <v>471</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.2">
@@ -7736,7 +7736,7 @@
         <v>472</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.2">
@@ -7744,7 +7744,7 @@
         <v>473</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.2">
@@ -7752,7 +7752,7 @@
         <v>474</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.2">
@@ -7760,7 +7760,7 @@
         <v>475</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.2">
@@ -7768,7 +7768,7 @@
         <v>476</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.2">
@@ -7776,7 +7776,7 @@
         <v>477</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.2">
@@ -7784,7 +7784,7 @@
         <v>478</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
@@ -7792,7 +7792,7 @@
         <v>479</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
@@ -7800,7 +7800,7 @@
         <v>480</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
@@ -7808,7 +7808,7 @@
         <v>481</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
@@ -7816,7 +7816,7 @@
         <v>482</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
@@ -7824,7 +7824,7 @@
         <v>483</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.2">
@@ -7832,7 +7832,7 @@
         <v>484</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.2">
@@ -7840,7 +7840,7 @@
         <v>485</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
@@ -7848,7 +7848,7 @@
         <v>486</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
@@ -7856,7 +7856,7 @@
         <v>487</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
@@ -7864,7 +7864,7 @@
         <v>488</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
@@ -7872,7 +7872,7 @@
         <v>489</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
@@ -7880,7 +7880,7 @@
         <v>490</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
@@ -7888,7 +7888,7 @@
         <v>491</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
@@ -7896,7 +7896,7 @@
         <v>492</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
@@ -7904,15 +7904,15 @@
         <v>493</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.2">
@@ -7920,7 +7920,7 @@
         <v>494</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.2">
@@ -7928,15 +7928,15 @@
         <v>495</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.2">
@@ -7944,7 +7944,7 @@
         <v>496</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.2">
@@ -7952,7 +7952,7 @@
         <v>497</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.2">
@@ -7960,7 +7960,7 @@
         <v>498</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.2">
@@ -7968,391 +7968,391 @@
         <v>499</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B522" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B523" t="s">
         <v>1009</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B524" t="s">
         <v>1011</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B525" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B526" t="s">
         <v>1025</v>
-      </c>
-      <c r="B526" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B527" t="s">
         <v>1027</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B528" t="s">
         <v>1030</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B529" t="s">
         <v>1036</v>
-      </c>
-      <c r="B529" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B530" t="s">
         <v>1038</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B531" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B532" t="s">
         <v>1046</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B533" t="s">
         <v>1048</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B534" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B535" t="s">
         <v>1054</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B536" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B537" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B538" t="s">
         <v>1060</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B539" t="s">
         <v>1062</v>
-      </c>
-      <c r="B539" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B540" t="s">
         <v>1064</v>
-      </c>
-      <c r="B540" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B541" t="s">
         <v>1066</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B542" t="s">
         <v>1068</v>
-      </c>
-      <c r="B542" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B543" t="s">
         <v>1070</v>
-      </c>
-      <c r="B543" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B544" t="s">
         <v>1072</v>
-      </c>
-      <c r="B544" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B545" t="s">
         <v>1074</v>
-      </c>
-      <c r="B545" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B546" t="s">
         <v>1076</v>
-      </c>
-      <c r="B546" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B547" t="s">
         <v>1078</v>
-      </c>
-      <c r="B547" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B548" t="s">
         <v>1080</v>
-      </c>
-      <c r="B548" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B549" t="s">
         <v>1082</v>
-      </c>
-      <c r="B549" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B550" t="s">
         <v>1084</v>
-      </c>
-      <c r="B550" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B551" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B552" t="s">
         <v>1088</v>
-      </c>
-      <c r="B552" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B553" t="s">
         <v>1091</v>
-      </c>
-      <c r="B553" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B554" t="s">
         <v>1096</v>
-      </c>
-      <c r="B554" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B555" t="s">
         <v>1094</v>
-      </c>
-      <c r="B555" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B556" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B557" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B558" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B559" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B560" t="s">
         <v>1107</v>
-      </c>
-      <c r="B560" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B561" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B562" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B563" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B564" t="s">
         <v>1116</v>
-      </c>
-      <c r="B564" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B565" t="s">
         <v>1118</v>
-      </c>
-      <c r="B565" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B566" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B567" t="s">
         <v>1124</v>
-      </c>
-      <c r="B567" t="s">
-        <v>1125</v>
       </c>
     </row>
   </sheetData>
@@ -8446,7 +8446,7 @@
     <hyperlink ref="B92" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
     <hyperlink ref="B93" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
     <hyperlink ref="B94" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="B95" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="B95" r:id="rId90" display="https://static.tildacdn.com/stor6230-3138-4833-b439-343538643038/19031351.jpg" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
     <hyperlink ref="B96" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
     <hyperlink ref="B97" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
     <hyperlink ref="B98" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BCAE9E-7975-1A48-8826-46B7B45CC572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78FA0C7-E8D3-8F44-BABE-FF630C8A67F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="1126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="1128">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3398,6 +3398,12 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor3638-6231-4432-b831-333763316336/-/format/webp/80741907.jpg</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor6133-3065-4230-a663-306632643232/-/format/webp/5bca1eb96bd12858f46963a97f868403.jpg</t>
+  </si>
+  <si>
+    <t>Directive 8020 PS5</t>
   </si>
 </sst>
 </file>
@@ -3812,7 +3818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B567"/>
+  <dimension ref="A1:B568"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8353,6 +8359,14 @@
       </c>
       <c r="B567" t="s">
         <v>1124</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A568" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1126</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78FA0C7-E8D3-8F44-BABE-FF630C8A67F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E04EC6-B4C9-1541-AC01-6B3DF85CA7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="1130">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3404,6 +3404,12 @@
   </si>
   <si>
     <t>Directive 8020 PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3334-6164-4335-b865-353538396435/-/format/webp/9a932f6027e76841e63c1758841db8c4.jpg</t>
+  </si>
+  <si>
+    <t>Mixtape PS5</t>
   </si>
 </sst>
 </file>
@@ -3818,7 +3824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B568"/>
+  <dimension ref="A1:B569"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8367,6 +8373,14 @@
       </c>
       <c r="B568" t="s">
         <v>1126</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A569" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1128</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E04EC6-B4C9-1541-AC01-6B3DF85CA7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0316A3C-A229-AA49-B17D-F9D0C94EC5FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2326,9 +2326,6 @@
     <t>https://static.tildacdn.com/stor3537-3737-4635-a535-643336663233/19172606.jpg</t>
   </si>
   <si>
-    <t>https://static.tildacdn.com/stor3030-6230-4230-a566-333630376238/19090300.jpg</t>
-  </si>
-  <si>
     <t>https://static.tildacdn.com/stor3430-6238-4430-b162-633431303163/31905856.jpg</t>
   </si>
   <si>
@@ -3410,6 +3407,9 @@
   </si>
   <si>
     <t>Mixtape PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3337-6232-4962-b864-393061653930/-/format/webp/52002318.jpg</t>
   </si>
 </sst>
 </file>
@@ -3833,10 +3833,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>984</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3908,7 +3908,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -4060,7 +4060,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -4081,7 +4081,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>528</v>
@@ -4089,7 +4089,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>528</v>
@@ -4100,7 +4100,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -4212,7 +4212,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -4241,7 +4241,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>545</v>
@@ -4324,7 +4324,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -4332,7 +4332,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -4353,7 +4353,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>557</v>
@@ -4380,7 +4380,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -4588,7 +4588,7 @@
         <v>89</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
@@ -4636,7 +4636,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
@@ -4729,7 +4729,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>601</v>
@@ -4788,12 +4788,12 @@
         <v>113</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>608</v>
@@ -4892,7 +4892,7 @@
         <v>125</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
@@ -4969,7 +4969,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>629</v>
@@ -5116,7 +5116,7 @@
         <v>152</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
@@ -5316,7 +5316,7 @@
         <v>177</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
@@ -5332,7 +5332,7 @@
         <v>179</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
@@ -5369,7 +5369,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>676</v>
@@ -5388,7 +5388,7 @@
         <v>185</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
@@ -5401,7 +5401,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>679</v>
@@ -5500,7 +5500,7 @@
         <v>198</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
@@ -5524,7 +5524,7 @@
         <v>201</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
@@ -5548,7 +5548,7 @@
         <v>204</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
@@ -5612,7 +5612,7 @@
         <v>212</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
@@ -5828,7 +5828,7 @@
         <v>239</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
@@ -6033,7 +6033,7 @@
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>753</v>
@@ -6113,10 +6113,10 @@
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B286" s="2" t="s">
         <v>1121</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
@@ -6164,7 +6164,7 @@
         <v>279</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>768</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
@@ -6172,7 +6172,7 @@
         <v>280</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
@@ -6180,7 +6180,7 @@
         <v>281</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
@@ -6188,7 +6188,7 @@
         <v>282</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
@@ -6196,7 +6196,7 @@
         <v>283</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
@@ -6204,7 +6204,7 @@
         <v>284</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
@@ -6212,7 +6212,7 @@
         <v>285</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
@@ -6220,7 +6220,7 @@
         <v>286</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
@@ -6228,7 +6228,7 @@
         <v>287</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
@@ -6236,7 +6236,7 @@
         <v>288</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
@@ -6244,7 +6244,7 @@
         <v>289</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
@@ -6252,7 +6252,7 @@
         <v>290</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
@@ -6260,7 +6260,7 @@
         <v>291</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
@@ -6268,7 +6268,7 @@
         <v>292</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
@@ -6276,7 +6276,7 @@
         <v>293</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
@@ -6284,7 +6284,7 @@
         <v>294</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
@@ -6292,7 +6292,7 @@
         <v>295</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
@@ -6300,7 +6300,7 @@
         <v>296</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
@@ -6308,7 +6308,7 @@
         <v>297</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
@@ -6316,7 +6316,7 @@
         <v>298</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
@@ -6324,7 +6324,7 @@
         <v>299</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
@@ -6332,7 +6332,7 @@
         <v>300</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
@@ -6340,7 +6340,7 @@
         <v>301</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
@@ -6348,7 +6348,7 @@
         <v>302</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
@@ -6356,7 +6356,7 @@
         <v>303</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
@@ -6364,7 +6364,7 @@
         <v>304</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
@@ -6372,7 +6372,7 @@
         <v>305</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
@@ -6380,7 +6380,7 @@
         <v>306</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
@@ -6388,7 +6388,7 @@
         <v>307</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
@@ -6396,7 +6396,7 @@
         <v>308</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
@@ -6404,7 +6404,7 @@
         <v>309</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
@@ -6412,7 +6412,7 @@
         <v>310</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
@@ -6428,7 +6428,7 @@
         <v>311</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
@@ -6436,7 +6436,7 @@
         <v>312</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
@@ -6444,7 +6444,7 @@
         <v>313</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
@@ -6452,7 +6452,7 @@
         <v>314</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
@@ -6460,7 +6460,7 @@
         <v>315</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
@@ -6468,7 +6468,7 @@
         <v>316</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
@@ -6476,7 +6476,7 @@
         <v>317</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
@@ -6484,7 +6484,7 @@
         <v>318</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
@@ -6492,7 +6492,7 @@
         <v>319</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
@@ -6500,7 +6500,7 @@
         <v>320</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
@@ -6508,7 +6508,7 @@
         <v>321</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
@@ -6516,7 +6516,7 @@
         <v>322</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
@@ -6524,7 +6524,7 @@
         <v>323</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
@@ -6532,7 +6532,7 @@
         <v>324</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
@@ -6540,7 +6540,7 @@
         <v>325</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
@@ -6548,7 +6548,7 @@
         <v>326</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
@@ -6556,7 +6556,7 @@
         <v>327</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
@@ -6564,7 +6564,7 @@
         <v>328</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
@@ -6572,7 +6572,7 @@
         <v>329</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
@@ -6580,7 +6580,7 @@
         <v>330</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
@@ -6588,7 +6588,7 @@
         <v>331</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
@@ -6596,7 +6596,7 @@
         <v>332</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
@@ -6604,7 +6604,7 @@
         <v>333</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
@@ -6612,7 +6612,7 @@
         <v>334</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.2">
@@ -6620,7 +6620,7 @@
         <v>335</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.2">
@@ -6628,7 +6628,7 @@
         <v>336</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
@@ -6636,7 +6636,7 @@
         <v>337</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.2">
@@ -6644,7 +6644,7 @@
         <v>338</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.2">
@@ -6652,7 +6652,7 @@
         <v>339</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.2">
@@ -6660,7 +6660,7 @@
         <v>340</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.2">
@@ -6668,7 +6668,7 @@
         <v>341</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.2">
@@ -6676,7 +6676,7 @@
         <v>342</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.2">
@@ -6684,7 +6684,7 @@
         <v>343</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.2">
@@ -6692,7 +6692,7 @@
         <v>344</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
@@ -6700,7 +6700,7 @@
         <v>345</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.2">
@@ -6708,7 +6708,7 @@
         <v>346</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.2">
@@ -6716,7 +6716,7 @@
         <v>347</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.2">
@@ -6724,7 +6724,7 @@
         <v>348</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.2">
@@ -6732,7 +6732,7 @@
         <v>349</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.2">
@@ -6740,7 +6740,7 @@
         <v>350</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.2">
@@ -6748,7 +6748,7 @@
         <v>6</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.2">
@@ -6756,7 +6756,7 @@
         <v>351</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
@@ -6764,7 +6764,7 @@
         <v>352</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.2">
@@ -6772,7 +6772,7 @@
         <v>353</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
@@ -6780,7 +6780,7 @@
         <v>354</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
@@ -6788,7 +6788,7 @@
         <v>355</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
@@ -6796,7 +6796,7 @@
         <v>356</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
@@ -6804,7 +6804,7 @@
         <v>357</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
@@ -6812,7 +6812,7 @@
         <v>358</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
@@ -6820,15 +6820,15 @@
         <v>359</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
@@ -6836,7 +6836,7 @@
         <v>360</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
@@ -6844,7 +6844,7 @@
         <v>361</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
@@ -6852,7 +6852,7 @@
         <v>362</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
@@ -6860,7 +6860,7 @@
         <v>363</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
@@ -6868,7 +6868,7 @@
         <v>364</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
@@ -6876,7 +6876,7 @@
         <v>365</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
@@ -6884,7 +6884,7 @@
         <v>366</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
@@ -6892,7 +6892,7 @@
         <v>367</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
@@ -6900,7 +6900,7 @@
         <v>368</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
@@ -6908,7 +6908,7 @@
         <v>369</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
@@ -6916,7 +6916,7 @@
         <v>370</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
@@ -6924,7 +6924,7 @@
         <v>371</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
@@ -6932,7 +6932,7 @@
         <v>372</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
@@ -6940,7 +6940,7 @@
         <v>373</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
@@ -6948,7 +6948,7 @@
         <v>374</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
@@ -6956,7 +6956,7 @@
         <v>375</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
@@ -6964,7 +6964,7 @@
         <v>376</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
@@ -6972,7 +6972,7 @@
         <v>377</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
@@ -6980,7 +6980,7 @@
         <v>378</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
@@ -6988,7 +6988,7 @@
         <v>379</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
@@ -6996,7 +6996,7 @@
         <v>380</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
@@ -7004,7 +7004,7 @@
         <v>381</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
@@ -7012,7 +7012,7 @@
         <v>382</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
@@ -7020,7 +7020,7 @@
         <v>383</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
@@ -7028,7 +7028,7 @@
         <v>384</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
@@ -7036,7 +7036,7 @@
         <v>385</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
@@ -7044,7 +7044,7 @@
         <v>386</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
@@ -7052,7 +7052,7 @@
         <v>387</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
@@ -7060,7 +7060,7 @@
         <v>388</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
@@ -7068,7 +7068,7 @@
         <v>389</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
@@ -7076,7 +7076,7 @@
         <v>390</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
@@ -7084,7 +7084,7 @@
         <v>391</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
@@ -7092,7 +7092,7 @@
         <v>392</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
@@ -7100,7 +7100,7 @@
         <v>393</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
@@ -7108,7 +7108,7 @@
         <v>394</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
@@ -7116,7 +7116,7 @@
         <v>395</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
@@ -7124,7 +7124,7 @@
         <v>396</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
@@ -7132,7 +7132,7 @@
         <v>397</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
@@ -7140,7 +7140,7 @@
         <v>398</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
@@ -7148,7 +7148,7 @@
         <v>399</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
@@ -7156,15 +7156,15 @@
         <v>400</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B417" s="2" t="s">
         <v>1016</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
@@ -7172,7 +7172,7 @@
         <v>401</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.2">
@@ -7180,7 +7180,7 @@
         <v>402</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
@@ -7188,7 +7188,7 @@
         <v>403</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.2">
@@ -7196,7 +7196,7 @@
         <v>404</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.2">
@@ -7204,7 +7204,7 @@
         <v>405</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.2">
@@ -7212,7 +7212,7 @@
         <v>406</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.2">
@@ -7220,7 +7220,7 @@
         <v>407</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
@@ -7228,7 +7228,7 @@
         <v>408</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.2">
@@ -7236,7 +7236,7 @@
         <v>409</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.2">
@@ -7244,7 +7244,7 @@
         <v>410</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
@@ -7252,7 +7252,7 @@
         <v>411</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.2">
@@ -7260,7 +7260,7 @@
         <v>412</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.2">
@@ -7268,7 +7268,7 @@
         <v>413</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.2">
@@ -7276,7 +7276,7 @@
         <v>414</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
@@ -7284,7 +7284,7 @@
         <v>415</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.2">
@@ -7292,7 +7292,7 @@
         <v>416</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.2">
@@ -7300,7 +7300,7 @@
         <v>417</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.2">
@@ -7308,7 +7308,7 @@
         <v>418</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.2">
@@ -7316,7 +7316,7 @@
         <v>419</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.2">
@@ -7324,7 +7324,7 @@
         <v>420</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.2">
@@ -7332,7 +7332,7 @@
         <v>421</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
@@ -7340,7 +7340,7 @@
         <v>422</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
@@ -7348,7 +7348,7 @@
         <v>423</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
@@ -7356,7 +7356,7 @@
         <v>424</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
@@ -7364,7 +7364,7 @@
         <v>425</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
@@ -7372,7 +7372,7 @@
         <v>426</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
@@ -7380,7 +7380,7 @@
         <v>427</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
@@ -7388,7 +7388,7 @@
         <v>428</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
@@ -7396,7 +7396,7 @@
         <v>429</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
@@ -7404,7 +7404,7 @@
         <v>430</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
@@ -7412,7 +7412,7 @@
         <v>431</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
@@ -7420,7 +7420,7 @@
         <v>432</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
@@ -7428,7 +7428,7 @@
         <v>433</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
@@ -7436,7 +7436,7 @@
         <v>434</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
@@ -7444,7 +7444,7 @@
         <v>435</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
@@ -7452,7 +7452,7 @@
         <v>436</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
@@ -7460,7 +7460,7 @@
         <v>437</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
@@ -7468,7 +7468,7 @@
         <v>438</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
@@ -7476,7 +7476,7 @@
         <v>439</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
@@ -7484,7 +7484,7 @@
         <v>440</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
@@ -7492,7 +7492,7 @@
         <v>441</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
@@ -7500,7 +7500,7 @@
         <v>442</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
@@ -7508,7 +7508,7 @@
         <v>443</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
@@ -7516,7 +7516,7 @@
         <v>444</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
@@ -7524,7 +7524,7 @@
         <v>445</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
@@ -7532,7 +7532,7 @@
         <v>446</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
@@ -7540,7 +7540,7 @@
         <v>447</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
@@ -7548,7 +7548,7 @@
         <v>448</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
@@ -7556,7 +7556,7 @@
         <v>449</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
@@ -7564,7 +7564,7 @@
         <v>450</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
@@ -7572,7 +7572,7 @@
         <v>451</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
@@ -7580,7 +7580,7 @@
         <v>452</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
@@ -7588,7 +7588,7 @@
         <v>453</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
@@ -7596,7 +7596,7 @@
         <v>454</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
@@ -7604,7 +7604,7 @@
         <v>455</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
@@ -7612,7 +7612,7 @@
         <v>456</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
@@ -7620,7 +7620,7 @@
         <v>457</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
@@ -7628,7 +7628,7 @@
         <v>458</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
@@ -7636,7 +7636,7 @@
         <v>459</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">
@@ -7644,7 +7644,7 @@
         <v>460</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
@@ -7652,7 +7652,7 @@
         <v>461</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
@@ -7660,7 +7660,7 @@
         <v>462</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
@@ -7668,7 +7668,7 @@
         <v>463</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.2">
@@ -7676,7 +7676,7 @@
         <v>464</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
@@ -7684,7 +7684,7 @@
         <v>465</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.2">
@@ -7692,15 +7692,15 @@
         <v>466</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.2">
@@ -7708,7 +7708,7 @@
         <v>467</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
@@ -7716,7 +7716,7 @@
         <v>468</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.2">
@@ -7724,7 +7724,7 @@
         <v>469</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.2">
@@ -7732,7 +7732,7 @@
         <v>470</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.2">
@@ -7740,7 +7740,7 @@
         <v>471</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.2">
@@ -7748,7 +7748,7 @@
         <v>472</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.2">
@@ -7756,7 +7756,7 @@
         <v>473</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.2">
@@ -7764,7 +7764,7 @@
         <v>474</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.2">
@@ -7772,7 +7772,7 @@
         <v>475</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.2">
@@ -7780,7 +7780,7 @@
         <v>476</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.2">
@@ -7788,7 +7788,7 @@
         <v>477</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.2">
@@ -7796,7 +7796,7 @@
         <v>478</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
@@ -7804,7 +7804,7 @@
         <v>479</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
@@ -7812,7 +7812,7 @@
         <v>480</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
@@ -7820,7 +7820,7 @@
         <v>481</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
@@ -7828,7 +7828,7 @@
         <v>482</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
@@ -7836,7 +7836,7 @@
         <v>483</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.2">
@@ -7844,7 +7844,7 @@
         <v>484</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.2">
@@ -7852,7 +7852,7 @@
         <v>485</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
@@ -7860,7 +7860,7 @@
         <v>486</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
@@ -7868,7 +7868,7 @@
         <v>487</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
@@ -7876,7 +7876,7 @@
         <v>488</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
@@ -7884,7 +7884,7 @@
         <v>489</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
@@ -7892,7 +7892,7 @@
         <v>490</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
@@ -7900,7 +7900,7 @@
         <v>491</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
@@ -7908,7 +7908,7 @@
         <v>492</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
@@ -7916,15 +7916,15 @@
         <v>493</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.2">
@@ -7932,7 +7932,7 @@
         <v>494</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.2">
@@ -7940,15 +7940,15 @@
         <v>495</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.2">
@@ -7956,7 +7956,7 @@
         <v>496</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.2">
@@ -7964,7 +7964,7 @@
         <v>497</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.2">
@@ -7972,7 +7972,7 @@
         <v>498</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.2">
@@ -7980,407 +7980,407 @@
         <v>499</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B522" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B523" t="s">
         <v>1008</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B524" t="s">
         <v>1010</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B525" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B526" t="s">
         <v>1024</v>
-      </c>
-      <c r="B526" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B527" t="s">
         <v>1026</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B528" t="s">
         <v>1029</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B529" t="s">
         <v>1035</v>
-      </c>
-      <c r="B529" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B530" t="s">
         <v>1037</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B531" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B532" t="s">
         <v>1045</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B533" t="s">
         <v>1047</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B534" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B535" t="s">
         <v>1053</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B536" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B537" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B538" t="s">
         <v>1059</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B539" t="s">
         <v>1061</v>
-      </c>
-      <c r="B539" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B540" t="s">
         <v>1063</v>
-      </c>
-      <c r="B540" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B541" t="s">
         <v>1065</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B542" t="s">
         <v>1067</v>
-      </c>
-      <c r="B542" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B543" t="s">
         <v>1069</v>
-      </c>
-      <c r="B543" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B544" t="s">
         <v>1071</v>
-      </c>
-      <c r="B544" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B545" t="s">
         <v>1073</v>
-      </c>
-      <c r="B545" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B546" t="s">
         <v>1075</v>
-      </c>
-      <c r="B546" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B547" t="s">
         <v>1077</v>
-      </c>
-      <c r="B547" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B548" t="s">
         <v>1079</v>
-      </c>
-      <c r="B548" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B549" t="s">
         <v>1081</v>
-      </c>
-      <c r="B549" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B550" t="s">
         <v>1083</v>
-      </c>
-      <c r="B550" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B551" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B552" t="s">
         <v>1087</v>
-      </c>
-      <c r="B552" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B553" t="s">
         <v>1090</v>
-      </c>
-      <c r="B553" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B554" t="s">
         <v>1095</v>
-      </c>
-      <c r="B554" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B555" t="s">
         <v>1093</v>
-      </c>
-      <c r="B555" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B556" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B557" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B558" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B559" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B560" t="s">
         <v>1106</v>
-      </c>
-      <c r="B560" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B561" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B562" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B563" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B564" t="s">
         <v>1115</v>
-      </c>
-      <c r="B564" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B565" t="s">
         <v>1117</v>
-      </c>
-      <c r="B565" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B566" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B567" t="s">
         <v>1123</v>
-      </c>
-      <c r="B567" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B568" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B569" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
   </sheetData>
@@ -8668,7 +8668,7 @@
     <hyperlink ref="B289" r:id="rId281" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
     <hyperlink ref="B290" r:id="rId282" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
     <hyperlink ref="B291" r:id="rId283" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="B292" r:id="rId284" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="B292" r:id="rId284" display="https://static.tildacdn.com/stor3030-6230-4230-a566-333630376238/19090300.jpg" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
     <hyperlink ref="B293" r:id="rId285" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
     <hyperlink ref="B294" r:id="rId286" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
     <hyperlink ref="B295" r:id="rId287" xr:uid="{00000000-0004-0000-0000-000024010000}"/>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0316A3C-A229-AA49-B17D-F9D0C94EC5FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E168659-EFBD-E34B-99BB-8763F6E7E5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="1132">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3410,6 +3410,12 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor3337-6232-4962-b864-393061653930/-/format/webp/52002318.jpg</t>
+  </si>
+  <si>
+    <t>https://static.tildacdn.com/stor3133-6134-4331-a632-316361396533/a386a17efa6184e68b024738664d324b.jpg</t>
+  </si>
+  <si>
+    <t>WILL: Follow The Light PS5</t>
   </si>
 </sst>
 </file>
@@ -3824,7 +3830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B569"/>
+  <dimension ref="A1:B570"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8381,6 +8387,14 @@
       </c>
       <c r="B569" t="s">
         <v>1127</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A570" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1130</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E168659-EFBD-E34B-99BB-8763F6E7E5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1B0D1B-0172-FE4D-B268-A11F2897979A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2035,9 +2035,6 @@
     <t>https://static.tildacdn.com/stor3034-3864-4830-b038-623538646232/54266530.jpg</t>
   </si>
   <si>
-    <t>https://static.tildacdn.com/stor3437-3336-4033-a263-613165376339/55249335.jpg</t>
-  </si>
-  <si>
     <t>https://static.tildacdn.com/stor3738-3632-4932-a363-373765383636/31820970.jpg</t>
   </si>
   <si>
@@ -3416,6 +3413,9 @@
   </si>
   <si>
     <t>WILL: Follow The Light PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor6634-6337-4434-a335-376231333837/-/format/webp/83659139.jpg</t>
   </si>
 </sst>
 </file>
@@ -3839,10 +3839,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>983</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3914,7 +3914,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -4066,7 +4066,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -4087,7 +4087,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>528</v>
@@ -4095,7 +4095,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>528</v>
@@ -4106,7 +4106,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -4218,7 +4218,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -4247,7 +4247,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>545</v>
@@ -4330,7 +4330,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -4338,7 +4338,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -4359,7 +4359,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>557</v>
@@ -4386,7 +4386,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -4594,7 +4594,7 @@
         <v>89</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
@@ -4642,7 +4642,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
@@ -4735,7 +4735,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>601</v>
@@ -4794,12 +4794,12 @@
         <v>113</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>608</v>
@@ -4898,7 +4898,7 @@
         <v>125</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
@@ -4975,7 +4975,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>629</v>
@@ -5122,7 +5122,7 @@
         <v>152</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
@@ -5322,7 +5322,7 @@
         <v>177</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
@@ -5330,7 +5330,7 @@
         <v>178</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>671</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
@@ -5338,7 +5338,7 @@
         <v>179</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
@@ -5346,7 +5346,7 @@
         <v>180</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
@@ -5354,7 +5354,7 @@
         <v>181</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
@@ -5362,7 +5362,7 @@
         <v>182</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
@@ -5370,15 +5370,15 @@
         <v>183</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
@@ -5386,7 +5386,7 @@
         <v>184</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
@@ -5394,7 +5394,7 @@
         <v>185</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
@@ -5402,15 +5402,15 @@
         <v>186</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
@@ -5418,7 +5418,7 @@
         <v>187</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
@@ -5426,7 +5426,7 @@
         <v>188</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
@@ -5434,7 +5434,7 @@
         <v>189</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
@@ -5442,7 +5442,7 @@
         <v>190</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
@@ -5450,7 +5450,7 @@
         <v>191</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
@@ -5458,7 +5458,7 @@
         <v>192</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
@@ -5466,7 +5466,7 @@
         <v>193</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
@@ -5474,7 +5474,7 @@
         <v>194</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
@@ -5482,7 +5482,7 @@
         <v>195</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
@@ -5490,7 +5490,7 @@
         <v>196</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
@@ -5498,7 +5498,7 @@
         <v>197</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
@@ -5506,7 +5506,7 @@
         <v>198</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
@@ -5514,7 +5514,7 @@
         <v>199</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
@@ -5522,7 +5522,7 @@
         <v>200</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
@@ -5530,7 +5530,7 @@
         <v>201</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
@@ -5538,7 +5538,7 @@
         <v>202</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
@@ -5546,7 +5546,7 @@
         <v>203</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
@@ -5554,7 +5554,7 @@
         <v>204</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
@@ -5562,7 +5562,7 @@
         <v>205</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
@@ -5570,7 +5570,7 @@
         <v>206</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
@@ -5578,7 +5578,7 @@
         <v>207</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
@@ -5586,7 +5586,7 @@
         <v>208</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
@@ -5594,7 +5594,7 @@
         <v>209</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
@@ -5602,7 +5602,7 @@
         <v>210</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
@@ -5610,7 +5610,7 @@
         <v>211</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
@@ -5618,7 +5618,7 @@
         <v>212</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
@@ -5626,7 +5626,7 @@
         <v>213</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
@@ -5634,7 +5634,7 @@
         <v>214</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
@@ -5642,7 +5642,7 @@
         <v>215</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
@@ -5650,7 +5650,7 @@
         <v>216</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
@@ -5658,7 +5658,7 @@
         <v>217</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
@@ -5666,7 +5666,7 @@
         <v>218</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
@@ -5674,7 +5674,7 @@
         <v>219</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
@@ -5682,7 +5682,7 @@
         <v>220</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
@@ -5690,7 +5690,7 @@
         <v>221</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
@@ -5698,7 +5698,7 @@
         <v>222</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
@@ -5706,7 +5706,7 @@
         <v>223</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
@@ -5714,7 +5714,7 @@
         <v>224</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
@@ -5722,7 +5722,7 @@
         <v>225</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
@@ -5730,7 +5730,7 @@
         <v>226</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
@@ -5738,7 +5738,7 @@
         <v>227</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
@@ -5746,7 +5746,7 @@
         <v>228</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
@@ -5754,7 +5754,7 @@
         <v>229</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
@@ -5762,7 +5762,7 @@
         <v>230</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
@@ -5770,7 +5770,7 @@
         <v>231</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
@@ -5778,7 +5778,7 @@
         <v>232</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
@@ -5786,7 +5786,7 @@
         <v>233</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
@@ -5794,7 +5794,7 @@
         <v>234</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
@@ -5802,7 +5802,7 @@
         <v>235</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
@@ -5810,7 +5810,7 @@
         <v>236</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
@@ -5818,7 +5818,7 @@
         <v>237</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
@@ -5826,7 +5826,7 @@
         <v>238</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
@@ -5834,7 +5834,7 @@
         <v>239</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
@@ -5842,7 +5842,7 @@
         <v>240</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
@@ -5850,7 +5850,7 @@
         <v>241</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
@@ -5858,7 +5858,7 @@
         <v>242</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
@@ -5866,7 +5866,7 @@
         <v>243</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
@@ -5874,7 +5874,7 @@
         <v>244</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
@@ -5882,7 +5882,7 @@
         <v>245</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
@@ -5890,7 +5890,7 @@
         <v>246</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
@@ -5898,7 +5898,7 @@
         <v>247</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
@@ -5906,7 +5906,7 @@
         <v>248</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
@@ -5914,7 +5914,7 @@
         <v>249</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
@@ -5922,7 +5922,7 @@
         <v>250</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
@@ -5930,7 +5930,7 @@
         <v>251</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
@@ -5938,7 +5938,7 @@
         <v>252</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
@@ -5946,7 +5946,7 @@
         <v>253</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
@@ -5954,7 +5954,7 @@
         <v>254</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
@@ -5962,7 +5962,7 @@
         <v>255</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
@@ -5970,7 +5970,7 @@
         <v>256</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
@@ -5978,7 +5978,7 @@
         <v>257</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
@@ -5986,7 +5986,7 @@
         <v>258</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
@@ -5994,7 +5994,7 @@
         <v>259</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
@@ -6002,7 +6002,7 @@
         <v>260</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
@@ -6010,7 +6010,7 @@
         <v>261</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
@@ -6018,7 +6018,7 @@
         <v>262</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
@@ -6026,7 +6026,7 @@
         <v>263</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
@@ -6034,15 +6034,15 @@
         <v>264</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
@@ -6050,7 +6050,7 @@
         <v>265</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
@@ -6058,7 +6058,7 @@
         <v>266</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
@@ -6066,7 +6066,7 @@
         <v>267</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
@@ -6074,7 +6074,7 @@
         <v>268</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
@@ -6082,7 +6082,7 @@
         <v>269</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
@@ -6090,7 +6090,7 @@
         <v>270</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
@@ -6098,7 +6098,7 @@
         <v>271</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
@@ -6106,7 +6106,7 @@
         <v>272</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
@@ -6114,15 +6114,15 @@
         <v>273</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B286" s="2" t="s">
         <v>1120</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
@@ -6130,7 +6130,7 @@
         <v>274</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
@@ -6138,7 +6138,7 @@
         <v>275</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
@@ -6146,7 +6146,7 @@
         <v>276</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
@@ -6154,7 +6154,7 @@
         <v>277</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
@@ -6162,7 +6162,7 @@
         <v>278</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
@@ -6170,7 +6170,7 @@
         <v>279</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
@@ -6178,7 +6178,7 @@
         <v>280</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
@@ -6186,7 +6186,7 @@
         <v>281</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
@@ -6194,7 +6194,7 @@
         <v>282</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
@@ -6202,7 +6202,7 @@
         <v>283</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
@@ -6210,7 +6210,7 @@
         <v>284</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
@@ -6218,7 +6218,7 @@
         <v>285</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
@@ -6226,7 +6226,7 @@
         <v>286</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
@@ -6234,7 +6234,7 @@
         <v>287</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
@@ -6242,7 +6242,7 @@
         <v>288</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
@@ -6250,7 +6250,7 @@
         <v>289</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
@@ -6258,7 +6258,7 @@
         <v>290</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
@@ -6266,7 +6266,7 @@
         <v>291</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
@@ -6274,7 +6274,7 @@
         <v>292</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
@@ -6282,7 +6282,7 @@
         <v>293</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
@@ -6290,7 +6290,7 @@
         <v>294</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
@@ -6298,7 +6298,7 @@
         <v>295</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
@@ -6306,7 +6306,7 @@
         <v>296</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
@@ -6314,7 +6314,7 @@
         <v>297</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
@@ -6322,7 +6322,7 @@
         <v>298</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
@@ -6330,7 +6330,7 @@
         <v>299</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
@@ -6338,7 +6338,7 @@
         <v>300</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
@@ -6346,7 +6346,7 @@
         <v>301</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
@@ -6354,7 +6354,7 @@
         <v>302</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
@@ -6362,7 +6362,7 @@
         <v>303</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
@@ -6370,7 +6370,7 @@
         <v>304</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
@@ -6378,7 +6378,7 @@
         <v>305</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
@@ -6386,7 +6386,7 @@
         <v>306</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
@@ -6394,7 +6394,7 @@
         <v>307</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
@@ -6402,7 +6402,7 @@
         <v>308</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
@@ -6410,7 +6410,7 @@
         <v>309</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
@@ -6418,7 +6418,7 @@
         <v>310</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
@@ -6434,7 +6434,7 @@
         <v>311</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
@@ -6442,7 +6442,7 @@
         <v>312</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
@@ -6450,7 +6450,7 @@
         <v>313</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
@@ -6458,7 +6458,7 @@
         <v>314</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
@@ -6466,7 +6466,7 @@
         <v>315</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
@@ -6474,7 +6474,7 @@
         <v>316</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
@@ -6482,7 +6482,7 @@
         <v>317</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
@@ -6490,7 +6490,7 @@
         <v>318</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
@@ -6498,7 +6498,7 @@
         <v>319</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
@@ -6506,7 +6506,7 @@
         <v>320</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
@@ -6514,7 +6514,7 @@
         <v>321</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
@@ -6522,7 +6522,7 @@
         <v>322</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
@@ -6530,7 +6530,7 @@
         <v>323</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
@@ -6538,7 +6538,7 @@
         <v>324</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
@@ -6546,7 +6546,7 @@
         <v>325</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
@@ -6554,7 +6554,7 @@
         <v>326</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
@@ -6562,7 +6562,7 @@
         <v>327</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
@@ -6570,7 +6570,7 @@
         <v>328</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
@@ -6578,7 +6578,7 @@
         <v>329</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
@@ -6586,7 +6586,7 @@
         <v>330</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
@@ -6594,7 +6594,7 @@
         <v>331</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
@@ -6602,7 +6602,7 @@
         <v>332</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
@@ -6610,7 +6610,7 @@
         <v>333</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
@@ -6618,7 +6618,7 @@
         <v>334</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.2">
@@ -6626,7 +6626,7 @@
         <v>335</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.2">
@@ -6634,7 +6634,7 @@
         <v>336</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
@@ -6642,7 +6642,7 @@
         <v>337</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.2">
@@ -6650,7 +6650,7 @@
         <v>338</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.2">
@@ -6658,7 +6658,7 @@
         <v>339</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.2">
@@ -6666,7 +6666,7 @@
         <v>340</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.2">
@@ -6674,7 +6674,7 @@
         <v>341</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.2">
@@ -6682,7 +6682,7 @@
         <v>342</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.2">
@@ -6690,7 +6690,7 @@
         <v>343</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.2">
@@ -6698,7 +6698,7 @@
         <v>344</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
@@ -6706,7 +6706,7 @@
         <v>345</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.2">
@@ -6714,7 +6714,7 @@
         <v>346</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.2">
@@ -6722,7 +6722,7 @@
         <v>347</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.2">
@@ -6730,7 +6730,7 @@
         <v>348</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.2">
@@ -6738,7 +6738,7 @@
         <v>349</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.2">
@@ -6746,7 +6746,7 @@
         <v>350</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.2">
@@ -6754,7 +6754,7 @@
         <v>6</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.2">
@@ -6762,7 +6762,7 @@
         <v>351</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
@@ -6770,7 +6770,7 @@
         <v>352</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.2">
@@ -6778,7 +6778,7 @@
         <v>353</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
@@ -6786,7 +6786,7 @@
         <v>354</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
@@ -6794,7 +6794,7 @@
         <v>355</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
@@ -6802,7 +6802,7 @@
         <v>356</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
@@ -6810,7 +6810,7 @@
         <v>357</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
@@ -6818,7 +6818,7 @@
         <v>358</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
@@ -6826,15 +6826,15 @@
         <v>359</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
@@ -6842,7 +6842,7 @@
         <v>360</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
@@ -6850,7 +6850,7 @@
         <v>361</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
@@ -6858,7 +6858,7 @@
         <v>362</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
@@ -6866,7 +6866,7 @@
         <v>363</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
@@ -6874,7 +6874,7 @@
         <v>364</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
@@ -6882,7 +6882,7 @@
         <v>365</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
@@ -6890,7 +6890,7 @@
         <v>366</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
@@ -6898,7 +6898,7 @@
         <v>367</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
@@ -6906,7 +6906,7 @@
         <v>368</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
@@ -6914,7 +6914,7 @@
         <v>369</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
@@ -6922,7 +6922,7 @@
         <v>370</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
@@ -6930,7 +6930,7 @@
         <v>371</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
@@ -6938,7 +6938,7 @@
         <v>372</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
@@ -6946,7 +6946,7 @@
         <v>373</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
@@ -6954,7 +6954,7 @@
         <v>374</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
@@ -6962,7 +6962,7 @@
         <v>375</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
@@ -6970,7 +6970,7 @@
         <v>376</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
@@ -6978,7 +6978,7 @@
         <v>377</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
@@ -6986,7 +6986,7 @@
         <v>378</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
@@ -6994,7 +6994,7 @@
         <v>379</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
@@ -7002,7 +7002,7 @@
         <v>380</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
@@ -7010,7 +7010,7 @@
         <v>381</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
@@ -7018,7 +7018,7 @@
         <v>382</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
@@ -7026,7 +7026,7 @@
         <v>383</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
@@ -7034,7 +7034,7 @@
         <v>384</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
@@ -7042,7 +7042,7 @@
         <v>385</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
@@ -7050,7 +7050,7 @@
         <v>386</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
@@ -7058,7 +7058,7 @@
         <v>387</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
@@ -7066,7 +7066,7 @@
         <v>388</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
@@ -7074,7 +7074,7 @@
         <v>389</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
@@ -7082,7 +7082,7 @@
         <v>390</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
@@ -7090,7 +7090,7 @@
         <v>391</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
@@ -7098,7 +7098,7 @@
         <v>392</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
@@ -7106,7 +7106,7 @@
         <v>393</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
@@ -7114,7 +7114,7 @@
         <v>394</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
@@ -7122,7 +7122,7 @@
         <v>395</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
@@ -7130,7 +7130,7 @@
         <v>396</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
@@ -7138,7 +7138,7 @@
         <v>397</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
@@ -7146,7 +7146,7 @@
         <v>398</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
@@ -7154,7 +7154,7 @@
         <v>399</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
@@ -7162,15 +7162,15 @@
         <v>400</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B417" s="2" t="s">
         <v>1015</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
@@ -7178,7 +7178,7 @@
         <v>401</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.2">
@@ -7186,7 +7186,7 @@
         <v>402</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
@@ -7194,7 +7194,7 @@
         <v>403</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.2">
@@ -7202,7 +7202,7 @@
         <v>404</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.2">
@@ -7210,7 +7210,7 @@
         <v>405</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.2">
@@ -7218,7 +7218,7 @@
         <v>406</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.2">
@@ -7226,7 +7226,7 @@
         <v>407</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
@@ -7234,7 +7234,7 @@
         <v>408</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.2">
@@ -7242,7 +7242,7 @@
         <v>409</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.2">
@@ -7250,7 +7250,7 @@
         <v>410</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
@@ -7258,7 +7258,7 @@
         <v>411</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.2">
@@ -7266,7 +7266,7 @@
         <v>412</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.2">
@@ -7274,7 +7274,7 @@
         <v>413</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.2">
@@ -7282,7 +7282,7 @@
         <v>414</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
@@ -7290,7 +7290,7 @@
         <v>415</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.2">
@@ -7298,7 +7298,7 @@
         <v>416</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.2">
@@ -7306,7 +7306,7 @@
         <v>417</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.2">
@@ -7314,7 +7314,7 @@
         <v>418</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.2">
@@ -7322,7 +7322,7 @@
         <v>419</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.2">
@@ -7330,7 +7330,7 @@
         <v>420</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.2">
@@ -7338,7 +7338,7 @@
         <v>421</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
@@ -7346,7 +7346,7 @@
         <v>422</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
@@ -7354,7 +7354,7 @@
         <v>423</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
@@ -7362,7 +7362,7 @@
         <v>424</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
@@ -7370,7 +7370,7 @@
         <v>425</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
@@ -7378,7 +7378,7 @@
         <v>426</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
@@ -7386,7 +7386,7 @@
         <v>427</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
@@ -7394,7 +7394,7 @@
         <v>428</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
@@ -7402,7 +7402,7 @@
         <v>429</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
@@ -7410,7 +7410,7 @@
         <v>430</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
@@ -7418,7 +7418,7 @@
         <v>431</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
@@ -7426,7 +7426,7 @@
         <v>432</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
@@ -7434,7 +7434,7 @@
         <v>433</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
@@ -7442,7 +7442,7 @@
         <v>434</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
@@ -7450,7 +7450,7 @@
         <v>435</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
@@ -7458,7 +7458,7 @@
         <v>436</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
@@ -7466,7 +7466,7 @@
         <v>437</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
@@ -7474,7 +7474,7 @@
         <v>438</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
@@ -7482,7 +7482,7 @@
         <v>439</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
@@ -7490,7 +7490,7 @@
         <v>440</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
@@ -7498,7 +7498,7 @@
         <v>441</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
@@ -7506,7 +7506,7 @@
         <v>442</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
@@ -7514,7 +7514,7 @@
         <v>443</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
@@ -7522,7 +7522,7 @@
         <v>444</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
@@ -7530,7 +7530,7 @@
         <v>445</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
@@ -7538,7 +7538,7 @@
         <v>446</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
@@ -7546,7 +7546,7 @@
         <v>447</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
@@ -7554,7 +7554,7 @@
         <v>448</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
@@ -7562,7 +7562,7 @@
         <v>449</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
@@ -7570,7 +7570,7 @@
         <v>450</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
@@ -7578,7 +7578,7 @@
         <v>451</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
@@ -7586,7 +7586,7 @@
         <v>452</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
@@ -7594,7 +7594,7 @@
         <v>453</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
@@ -7602,7 +7602,7 @@
         <v>454</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
@@ -7610,7 +7610,7 @@
         <v>455</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
@@ -7618,7 +7618,7 @@
         <v>456</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
@@ -7626,7 +7626,7 @@
         <v>457</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
@@ -7634,7 +7634,7 @@
         <v>458</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
@@ -7642,7 +7642,7 @@
         <v>459</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">
@@ -7650,7 +7650,7 @@
         <v>460</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
@@ -7658,7 +7658,7 @@
         <v>461</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
@@ -7666,7 +7666,7 @@
         <v>462</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
@@ -7674,7 +7674,7 @@
         <v>463</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.2">
@@ -7682,7 +7682,7 @@
         <v>464</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
@@ -7690,7 +7690,7 @@
         <v>465</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.2">
@@ -7698,15 +7698,15 @@
         <v>466</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.2">
@@ -7714,7 +7714,7 @@
         <v>467</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
@@ -7722,7 +7722,7 @@
         <v>468</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.2">
@@ -7730,7 +7730,7 @@
         <v>469</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.2">
@@ -7738,7 +7738,7 @@
         <v>470</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.2">
@@ -7746,7 +7746,7 @@
         <v>471</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.2">
@@ -7754,7 +7754,7 @@
         <v>472</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.2">
@@ -7762,7 +7762,7 @@
         <v>473</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.2">
@@ -7770,7 +7770,7 @@
         <v>474</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.2">
@@ -7778,7 +7778,7 @@
         <v>475</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.2">
@@ -7786,7 +7786,7 @@
         <v>476</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.2">
@@ -7794,7 +7794,7 @@
         <v>477</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.2">
@@ -7802,7 +7802,7 @@
         <v>478</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
@@ -7810,7 +7810,7 @@
         <v>479</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
@@ -7818,7 +7818,7 @@
         <v>480</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
@@ -7826,7 +7826,7 @@
         <v>481</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
@@ -7834,7 +7834,7 @@
         <v>482</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
@@ -7842,7 +7842,7 @@
         <v>483</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.2">
@@ -7850,7 +7850,7 @@
         <v>484</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.2">
@@ -7858,7 +7858,7 @@
         <v>485</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
@@ -7866,7 +7866,7 @@
         <v>486</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
@@ -7874,7 +7874,7 @@
         <v>487</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
@@ -7882,7 +7882,7 @@
         <v>488</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
@@ -7890,7 +7890,7 @@
         <v>489</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
@@ -7898,7 +7898,7 @@
         <v>490</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
@@ -7906,7 +7906,7 @@
         <v>491</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
@@ -7914,7 +7914,7 @@
         <v>492</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
@@ -7922,15 +7922,15 @@
         <v>493</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.2">
@@ -7938,7 +7938,7 @@
         <v>494</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.2">
@@ -7946,15 +7946,15 @@
         <v>495</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.2">
@@ -7962,7 +7962,7 @@
         <v>496</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.2">
@@ -7970,7 +7970,7 @@
         <v>497</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.2">
@@ -7978,7 +7978,7 @@
         <v>498</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.2">
@@ -7986,415 +7986,415 @@
         <v>499</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B522" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B523" t="s">
         <v>1007</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B524" t="s">
         <v>1009</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B525" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B526" t="s">
         <v>1023</v>
-      </c>
-      <c r="B526" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B527" t="s">
         <v>1025</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B528" t="s">
         <v>1028</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B529" t="s">
         <v>1034</v>
-      </c>
-      <c r="B529" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B530" t="s">
         <v>1036</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B531" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B532" t="s">
         <v>1044</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B533" t="s">
         <v>1046</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B534" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B535" t="s">
         <v>1052</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B536" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B537" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B538" t="s">
         <v>1058</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B539" t="s">
         <v>1060</v>
-      </c>
-      <c r="B539" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B540" t="s">
         <v>1062</v>
-      </c>
-      <c r="B540" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B541" t="s">
         <v>1064</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B542" t="s">
         <v>1066</v>
-      </c>
-      <c r="B542" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B543" t="s">
         <v>1068</v>
-      </c>
-      <c r="B543" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B544" t="s">
         <v>1070</v>
-      </c>
-      <c r="B544" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B545" t="s">
         <v>1072</v>
-      </c>
-      <c r="B545" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B546" t="s">
         <v>1074</v>
-      </c>
-      <c r="B546" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B547" t="s">
         <v>1076</v>
-      </c>
-      <c r="B547" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B548" t="s">
         <v>1078</v>
-      </c>
-      <c r="B548" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B549" t="s">
         <v>1080</v>
-      </c>
-      <c r="B549" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B550" t="s">
         <v>1082</v>
-      </c>
-      <c r="B550" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B551" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B552" t="s">
         <v>1086</v>
-      </c>
-      <c r="B552" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B553" t="s">
         <v>1089</v>
-      </c>
-      <c r="B553" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B554" t="s">
         <v>1094</v>
-      </c>
-      <c r="B554" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B555" t="s">
         <v>1092</v>
-      </c>
-      <c r="B555" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B556" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B557" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B558" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B559" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B560" t="s">
         <v>1105</v>
-      </c>
-      <c r="B560" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B561" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B562" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B563" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B564" t="s">
         <v>1114</v>
-      </c>
-      <c r="B564" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B565" t="s">
         <v>1116</v>
-      </c>
-      <c r="B565" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B566" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B567" t="s">
         <v>1122</v>
-      </c>
-      <c r="B567" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B568" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B569" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B570" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
   </sheetData>
@@ -8578,7 +8578,7 @@
     <hyperlink ref="B183" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
     <hyperlink ref="B184" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
     <hyperlink ref="B185" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="B187" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="B187" r:id="rId180" display="https://static.tildacdn.com/stor3437-3336-4033-a263-613165376339/55249335.jpg" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
     <hyperlink ref="B188" r:id="rId181" display="https://static.tildacdn.com/stor6132-3834-4436-b731-643665643965/22019043.jpg" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
     <hyperlink ref="B189" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
     <hyperlink ref="B190" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1B0D1B-0172-FE4D-B268-A11F2897979A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD82F8E6-350C-E347-A0C5-2179F03A3A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="27160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2545,9 +2545,6 @@
     <t>https://static.tildacdn.com/stor3731-3465-4631-b432-623238333731/89548638.png</t>
   </si>
   <si>
-    <t>https://static.tildacdn.com/stor3464-6437-4865-b632-386539323330/93244129.jpg</t>
-  </si>
-  <si>
     <t>https://static.tildacdn.com/stor6638-6666-4034-a533-326133326234/46285791.jpg</t>
   </si>
   <si>
@@ -2593,9 +2590,6 @@
     <t>https://static.tildacdn.com/stor3639-3639-4534-b561-646337323965/93568558.jpg</t>
   </si>
   <si>
-    <t>https://static.tildacdn.com/stor3662-3436-4465-a337-393736346139/62406870.jpg</t>
-  </si>
-  <si>
     <t>https://static.tildacdn.com/stor6463-6137-4535-b338-306130383663/15638724.jpg</t>
   </si>
   <si>
@@ -3416,6 +3410,12 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor6634-6337-4434-a335-376231333837/-/format/webp/83659139.jpg</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor6436-3831-4664-b534-336239306536/-/format/webp/17860203.jpg</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor6262-3333-4231-a264-623163306433/-/format/webp/82501665.jpg</t>
   </si>
 </sst>
 </file>
@@ -3839,10 +3839,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3914,7 +3914,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -4066,7 +4066,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -4087,7 +4087,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>528</v>
@@ -4095,7 +4095,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>528</v>
@@ -4106,7 +4106,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -4218,7 +4218,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -4247,7 +4247,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>545</v>
@@ -4330,7 +4330,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -4338,7 +4338,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -4359,7 +4359,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>557</v>
@@ -4386,7 +4386,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -4594,7 +4594,7 @@
         <v>89</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
@@ -4642,7 +4642,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
@@ -4735,7 +4735,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>601</v>
@@ -4794,12 +4794,12 @@
         <v>113</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>608</v>
@@ -4898,7 +4898,7 @@
         <v>125</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
@@ -4975,7 +4975,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>629</v>
@@ -5122,7 +5122,7 @@
         <v>152</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
@@ -5322,7 +5322,7 @@
         <v>177</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
@@ -5330,7 +5330,7 @@
         <v>178</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
@@ -5338,7 +5338,7 @@
         <v>179</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
@@ -5375,7 +5375,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>675</v>
@@ -5394,7 +5394,7 @@
         <v>185</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
@@ -5407,7 +5407,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>678</v>
@@ -5506,7 +5506,7 @@
         <v>198</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
@@ -5530,7 +5530,7 @@
         <v>201</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
@@ -5554,7 +5554,7 @@
         <v>204</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
@@ -5618,7 +5618,7 @@
         <v>212</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
@@ -5834,7 +5834,7 @@
         <v>239</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
@@ -6039,7 +6039,7 @@
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>752</v>
@@ -6119,10 +6119,10 @@
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
@@ -6170,7 +6170,7 @@
         <v>279</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
@@ -6778,7 +6778,7 @@
         <v>353</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>841</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
@@ -6786,7 +6786,7 @@
         <v>354</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
@@ -6794,7 +6794,7 @@
         <v>355</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
@@ -6802,7 +6802,7 @@
         <v>356</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
@@ -6810,7 +6810,7 @@
         <v>357</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
@@ -6818,7 +6818,7 @@
         <v>358</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
@@ -6826,15 +6826,15 @@
         <v>359</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
@@ -6842,7 +6842,7 @@
         <v>360</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
@@ -6850,7 +6850,7 @@
         <v>361</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
@@ -6858,7 +6858,7 @@
         <v>362</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
@@ -6866,7 +6866,7 @@
         <v>363</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
@@ -6874,7 +6874,7 @@
         <v>364</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
@@ -6882,7 +6882,7 @@
         <v>365</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
@@ -6890,7 +6890,7 @@
         <v>366</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
@@ -6898,7 +6898,7 @@
         <v>367</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
@@ -6906,7 +6906,7 @@
         <v>368</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
@@ -6914,7 +6914,7 @@
         <v>369</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
@@ -6922,7 +6922,7 @@
         <v>370</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>857</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
@@ -6930,7 +6930,7 @@
         <v>371</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
@@ -6938,7 +6938,7 @@
         <v>372</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
@@ -6946,7 +6946,7 @@
         <v>373</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
@@ -6954,7 +6954,7 @@
         <v>374</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
@@ -6962,7 +6962,7 @@
         <v>375</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
@@ -6970,7 +6970,7 @@
         <v>376</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
@@ -6978,7 +6978,7 @@
         <v>377</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
@@ -6986,7 +6986,7 @@
         <v>378</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
@@ -6994,7 +6994,7 @@
         <v>379</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
@@ -7002,7 +7002,7 @@
         <v>380</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
@@ -7010,7 +7010,7 @@
         <v>381</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
@@ -7018,7 +7018,7 @@
         <v>382</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
@@ -7026,7 +7026,7 @@
         <v>383</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
@@ -7034,7 +7034,7 @@
         <v>384</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
@@ -7042,7 +7042,7 @@
         <v>385</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
@@ -7050,7 +7050,7 @@
         <v>386</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
@@ -7058,7 +7058,7 @@
         <v>387</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
@@ -7066,7 +7066,7 @@
         <v>388</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
@@ -7074,7 +7074,7 @@
         <v>389</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
@@ -7082,7 +7082,7 @@
         <v>390</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
@@ -7090,7 +7090,7 @@
         <v>391</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
@@ -7098,7 +7098,7 @@
         <v>392</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
@@ -7106,7 +7106,7 @@
         <v>393</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
@@ -7114,7 +7114,7 @@
         <v>394</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
@@ -7122,7 +7122,7 @@
         <v>395</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
@@ -7130,7 +7130,7 @@
         <v>396</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
@@ -7138,7 +7138,7 @@
         <v>397</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
@@ -7146,7 +7146,7 @@
         <v>398</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
@@ -7154,7 +7154,7 @@
         <v>399</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
@@ -7162,15 +7162,15 @@
         <v>400</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
@@ -7178,7 +7178,7 @@
         <v>401</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.2">
@@ -7186,7 +7186,7 @@
         <v>402</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
@@ -7194,7 +7194,7 @@
         <v>403</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.2">
@@ -7202,7 +7202,7 @@
         <v>404</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.2">
@@ -7210,7 +7210,7 @@
         <v>405</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.2">
@@ -7218,7 +7218,7 @@
         <v>406</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.2">
@@ -7226,7 +7226,7 @@
         <v>407</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
@@ -7234,7 +7234,7 @@
         <v>408</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.2">
@@ -7242,7 +7242,7 @@
         <v>409</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.2">
@@ -7250,7 +7250,7 @@
         <v>410</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
@@ -7258,7 +7258,7 @@
         <v>411</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.2">
@@ -7266,7 +7266,7 @@
         <v>412</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.2">
@@ -7274,7 +7274,7 @@
         <v>413</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.2">
@@ -7282,7 +7282,7 @@
         <v>414</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
@@ -7290,7 +7290,7 @@
         <v>415</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.2">
@@ -7298,7 +7298,7 @@
         <v>416</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.2">
@@ -7306,7 +7306,7 @@
         <v>417</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.2">
@@ -7314,7 +7314,7 @@
         <v>418</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.2">
@@ -7322,7 +7322,7 @@
         <v>419</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.2">
@@ -7330,7 +7330,7 @@
         <v>420</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.2">
@@ -7338,7 +7338,7 @@
         <v>421</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
@@ -7346,7 +7346,7 @@
         <v>422</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
@@ -7354,7 +7354,7 @@
         <v>423</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
@@ -7362,7 +7362,7 @@
         <v>424</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
@@ -7370,7 +7370,7 @@
         <v>425</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
@@ -7378,7 +7378,7 @@
         <v>426</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
@@ -7386,7 +7386,7 @@
         <v>427</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
@@ -7394,7 +7394,7 @@
         <v>428</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
@@ -7402,7 +7402,7 @@
         <v>429</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
@@ -7410,7 +7410,7 @@
         <v>430</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
@@ -7418,7 +7418,7 @@
         <v>431</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
@@ -7426,7 +7426,7 @@
         <v>432</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
@@ -7434,7 +7434,7 @@
         <v>433</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
@@ -7442,7 +7442,7 @@
         <v>434</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
@@ -7450,7 +7450,7 @@
         <v>435</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
@@ -7458,7 +7458,7 @@
         <v>436</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
@@ -7466,7 +7466,7 @@
         <v>437</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
@@ -7474,7 +7474,7 @@
         <v>438</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
@@ -7482,7 +7482,7 @@
         <v>439</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
@@ -7490,7 +7490,7 @@
         <v>440</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
@@ -7498,7 +7498,7 @@
         <v>441</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
@@ -7506,7 +7506,7 @@
         <v>442</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
@@ -7514,7 +7514,7 @@
         <v>443</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
@@ -7522,7 +7522,7 @@
         <v>444</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
@@ -7530,7 +7530,7 @@
         <v>445</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
@@ -7538,7 +7538,7 @@
         <v>446</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
@@ -7546,7 +7546,7 @@
         <v>447</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
@@ -7554,7 +7554,7 @@
         <v>448</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
@@ -7562,7 +7562,7 @@
         <v>449</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
@@ -7570,7 +7570,7 @@
         <v>450</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
@@ -7578,7 +7578,7 @@
         <v>451</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
@@ -7586,7 +7586,7 @@
         <v>452</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
@@ -7594,7 +7594,7 @@
         <v>453</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
@@ -7602,7 +7602,7 @@
         <v>454</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
@@ -7610,7 +7610,7 @@
         <v>455</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
@@ -7618,7 +7618,7 @@
         <v>456</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
@@ -7626,7 +7626,7 @@
         <v>457</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
@@ -7634,7 +7634,7 @@
         <v>458</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
@@ -7642,7 +7642,7 @@
         <v>459</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">
@@ -7650,7 +7650,7 @@
         <v>460</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
@@ -7658,7 +7658,7 @@
         <v>461</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
@@ -7666,7 +7666,7 @@
         <v>462</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
@@ -7674,7 +7674,7 @@
         <v>463</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.2">
@@ -7682,7 +7682,7 @@
         <v>464</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
@@ -7690,7 +7690,7 @@
         <v>465</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.2">
@@ -7698,15 +7698,15 @@
         <v>466</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.2">
@@ -7714,7 +7714,7 @@
         <v>467</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
@@ -7722,7 +7722,7 @@
         <v>468</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.2">
@@ -7730,7 +7730,7 @@
         <v>469</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.2">
@@ -7738,7 +7738,7 @@
         <v>470</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.2">
@@ -7746,7 +7746,7 @@
         <v>471</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.2">
@@ -7754,7 +7754,7 @@
         <v>472</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.2">
@@ -7762,7 +7762,7 @@
         <v>473</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.2">
@@ -7770,7 +7770,7 @@
         <v>474</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.2">
@@ -7778,7 +7778,7 @@
         <v>475</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.2">
@@ -7786,7 +7786,7 @@
         <v>476</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.2">
@@ -7794,7 +7794,7 @@
         <v>477</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.2">
@@ -7802,7 +7802,7 @@
         <v>478</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
@@ -7810,7 +7810,7 @@
         <v>479</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
@@ -7818,7 +7818,7 @@
         <v>480</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
@@ -7826,7 +7826,7 @@
         <v>481</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
@@ -7834,7 +7834,7 @@
         <v>482</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
@@ -7842,7 +7842,7 @@
         <v>483</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.2">
@@ -7850,7 +7850,7 @@
         <v>484</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.2">
@@ -7858,7 +7858,7 @@
         <v>485</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
@@ -7866,7 +7866,7 @@
         <v>486</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
@@ -7874,7 +7874,7 @@
         <v>487</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
@@ -7882,7 +7882,7 @@
         <v>488</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
@@ -7890,7 +7890,7 @@
         <v>489</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
@@ -7898,7 +7898,7 @@
         <v>490</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
@@ -7906,7 +7906,7 @@
         <v>491</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
@@ -7914,7 +7914,7 @@
         <v>492</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
@@ -7922,15 +7922,15 @@
         <v>493</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.2">
@@ -7938,7 +7938,7 @@
         <v>494</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.2">
@@ -7946,15 +7946,15 @@
         <v>495</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.2">
@@ -7962,7 +7962,7 @@
         <v>496</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.2">
@@ -7970,7 +7970,7 @@
         <v>497</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.2">
@@ -7978,7 +7978,7 @@
         <v>498</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.2">
@@ -7986,415 +7986,415 @@
         <v>499</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B522" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B523" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B524" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B525" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B526" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B527" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B528" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B529" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B530" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B531" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B532" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B533" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B534" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B535" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B536" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B537" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B538" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="B539" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B540" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="B541" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B542" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B543" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B544" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B545" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="B546" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B547" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B548" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B549" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B550" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="B551" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="B552" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B553" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B554" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B555" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B556" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B557" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B558" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="B559" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B560" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B561" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="B562" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B563" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="B564" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="B565" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="B566" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B567" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B568" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="B569" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B570" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
     </row>
   </sheetData>
@@ -8758,7 +8758,7 @@
     <hyperlink ref="B365" r:id="rId357" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
     <hyperlink ref="B366" r:id="rId358" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
     <hyperlink ref="B367" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="B368" r:id="rId360" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="B368" r:id="rId360" display="https://static.tildacdn.com/stor3464-6437-4865-b632-386539323330/93244129.jpg" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
     <hyperlink ref="B369" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
     <hyperlink ref="B370" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
     <hyperlink ref="B371" r:id="rId363" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
@@ -8776,7 +8776,7 @@
     <hyperlink ref="B383" r:id="rId375" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
     <hyperlink ref="B384" r:id="rId376" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
     <hyperlink ref="B385" r:id="rId377" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="B386" r:id="rId378" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="B386" r:id="rId378" display="https://static.tildacdn.com/stor3662-3436-4465-a337-393736346139/62406870.jpg" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
     <hyperlink ref="B387" r:id="rId379" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
     <hyperlink ref="B388" r:id="rId380" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
     <hyperlink ref="B389" r:id="rId381" xr:uid="{00000000-0004-0000-0000-000082010000}"/>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD82F8E6-350C-E347-A0C5-2179F03A3A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6C8BED-D9E8-FB49-9898-0DFA40C89848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="27160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="1132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="1134">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3416,6 +3416,12 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor6262-3333-4231-a264-623163306433/-/format/webp/82501665.jpg</t>
+  </si>
+  <si>
+    <t>LEGO BATMAN: Наследие Темного рыцаря PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor6232-6630-4163-b061-303434633632/-/format/webp/c609a2fc000cf8fe48127e14e78e5282.jpg</t>
   </si>
 </sst>
 </file>
@@ -3830,7 +3836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B570"/>
+  <dimension ref="A1:B571"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8395,6 +8401,14 @@
       </c>
       <c r="B570" t="s">
         <v>1127</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A571" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1133</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6C8BED-D9E8-FB49-9898-0DFA40C89848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D131E544-C46D-3342-ACD2-1EA0BE871F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="1136">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3422,6 +3422,12 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor6232-6630-4163-b061-303434633632/-/format/webp/c609a2fc000cf8fe48127e14e78e5282.jpg</t>
+  </si>
+  <si>
+    <t>Gothic 1 Remake PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor6663-3664-4330-a633-393461343038/-/format/webp/7473c0a2e525e9c047b11797d7151a27.jpg</t>
   </si>
 </sst>
 </file>
@@ -3836,7 +3842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B571"/>
+  <dimension ref="A1:B572"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8409,6 +8415,14 @@
       </c>
       <c r="B571" t="s">
         <v>1133</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A572" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B572" t="s">
+        <v>1135</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D131E544-C46D-3342-ACD2-1EA0BE871F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9495FAC-4722-F54B-9588-4D50A07FE29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="1136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="1140">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3428,6 +3428,18 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor6663-3664-4330-a633-393461343038/-/format/webp/7473c0a2e525e9c047b11797d7151a27.jpg</t>
+  </si>
+  <si>
+    <t>Assassin's Creed Black Flag Resynced PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3532-3336-4262-b531-303639386434/-/format/webp/7e2f64a2b04320f078848a0632cc8f41.jpg</t>
+  </si>
+  <si>
+    <t>Bo: Path of the Teal Lotus PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3962-3032-4565-a465-643266616465/-/format/webp/12797932.jpg</t>
   </si>
 </sst>
 </file>
@@ -3842,7 +3854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B572"/>
+  <dimension ref="A1:B574"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8423,6 +8435,22 @@
       </c>
       <c r="B572" t="s">
         <v>1135</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A573" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B573" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A574" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B574" t="s">
+        <v>1139</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9495FAC-4722-F54B-9588-4D50A07FE29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6D596F-64E3-8C4E-9818-ABBB6A33F975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="1142">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3440,6 +3440,12 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor3962-3032-4565-a465-643266616465/-/format/webp/12797932.jpg</t>
+  </si>
+  <si>
+    <t>DOOM: The Dark Ages Revelations PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor6237-3539-4662-a338-323736336166/-/format/webp/5777ab8f3e68502e9ff025dfcc4050ff.jpg</t>
   </si>
 </sst>
 </file>
@@ -3854,7 +3860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B574"/>
+  <dimension ref="A1:B575"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8451,6 +8457,14 @@
       </c>
       <c r="B574" t="s">
         <v>1139</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A575" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B575" t="s">
+        <v>1141</v>
       </c>
     </row>
   </sheetData>

--- a/Названия_и_первая_картинка.xlsx
+++ b/Названия_и_первая_картинка.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrijsmit/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6D596F-64E3-8C4E-9818-ABBB6A33F975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D66B6F5-440E-BD4A-9280-7125ACE4B00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="1142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="1146">
   <si>
     <t>Star Wars Outlaws PS5</t>
   </si>
@@ -3446,6 +3446,18 @@
   </si>
   <si>
     <t>https://optim.tildacdn.com/stor6237-3539-4662-a338-323736336166/-/format/webp/5777ab8f3e68502e9ff025dfcc4050ff.jpg</t>
+  </si>
+  <si>
+    <t>Call of Duty: Black Ops PS4/PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3335-3064-4631-a139-333961646264/-/format/webp/9617b41c42173f3e38b5d23dbbc0b235.jpg</t>
+  </si>
+  <si>
+    <t>Call of Duty: Black Ops II PS4/PS5</t>
+  </si>
+  <si>
+    <t>https://optim.tildacdn.com/stor3833-6364-4234-b233-346334633863/-/format/webp/59077c484b88d59af4552d0f13a3ae89.jpg</t>
   </si>
 </sst>
 </file>
@@ -3860,7 +3872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B575"/>
+  <dimension ref="A1:B577"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -8465,6 +8477,22 @@
       </c>
       <c r="B575" t="s">
         <v>1141</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A576" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B576" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A577" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B577" t="s">
+        <v>1145</v>
       </c>
     </row>
   </sheetData>
